--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:X101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,20 +521,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>origin_country</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>production_companies</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>production_countries</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>spoken_languages</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>homepage</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>tagline</t>
         </is>
@@ -573,7 +583,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>137.751</v>
+        <v>5.167</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -594,10 +604,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>7.608</v>
+        <v>7.606</v>
       </c>
       <c r="N2" t="n">
-        <v>12294</v>
+        <v>12339</v>
       </c>
       <c r="O2" t="n">
         <v>460000000</v>
@@ -615,20 +625,30 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>['20th Century Studios', 'Lightstorm Entertainment']</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>https://www.20thcenturystudiosla.com/peliculas/avatar-el-camino-del-agua</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Esta familia es nuestro fuerte.</t>
         </is>
@@ -667,7 +687,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>159.864</v>
+        <v>5.295</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -688,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.9</v>
+        <v>7.948</v>
       </c>
       <c r="N3" t="n">
-        <v>20552</v>
+        <v>20589</v>
       </c>
       <c r="O3" t="n">
         <v>200000000</v>
@@ -709,20 +729,30 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>['Marvel Studios', 'Pascal Pictures', 'Columbia Pictures']</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>['English', '']</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>https://www.sonypictures.com.mx/movies/spider-man-sin-camino-casa</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Un gran poder conlleva una gran responsabilidad.</t>
         </is>
@@ -761,7 +791,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>334.444</v>
+        <v>5.305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -782,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="N4" t="n">
-        <v>5583</v>
+        <v>5647</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -803,20 +833,30 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures', 'Pixar']</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>https://www.disneylatino.com/peliculas/intensamente-2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Hagan espacio para nuevas emociones.</t>
         </is>
@@ -855,7 +895,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>184.313</v>
+        <v>5.948</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -876,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.186</v>
+        <v>8.183999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9605</v>
+        <v>9646</v>
       </c>
       <c r="O5" t="n">
         <v>170000000</v>
@@ -897,16 +937,26 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>['Skydance Media', 'Don Simpson/Jerry Bruckheimer Films', 'Paramount Pictures']</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Siente la necesidad... La necesidad de velocidad.</t>
         </is>
@@ -918,7 +968,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/3N5QNUqS76GFYNoEayfkkJyAyTN.jpg</t>
+          <t>/mbYTRO33LJAgpCMrIn9ibiWHbMH.jpg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -945,7 +995,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>121.814</v>
+        <v>5.677</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -966,10 +1016,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.984</v>
+        <v>6.982</v>
       </c>
       <c r="N6" t="n">
-        <v>9597</v>
+        <v>9666</v>
       </c>
       <c r="O6" t="n">
         <v>145000000</v>
@@ -987,20 +1037,30 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>['LuckyChap Entertainment', 'Heyday Films', 'NB/GG Pictures', 'Mattel', 'Warner Bros. Pictures']</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>https://www.warnerbroslatino.com/es-mx/peliculas/barbie</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Ella lo es todo. Él es solo Ken.</t>
         </is>
@@ -1039,7 +1099,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>163.339</v>
+        <v>4.845</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1060,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.632</v>
+        <v>7.627</v>
       </c>
       <c r="N7" t="n">
-        <v>9476</v>
+        <v>9517</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1081,20 +1141,30 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Illumination', 'Nintendo']</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>['Japan', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>https://www.universalpictures.com.mx/micro/super-mario-bros</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>No todos los héroes usan capa. Algunos usan manos.</t>
         </is>
@@ -1133,7 +1203,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>368.88</v>
+        <v>5.328</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1154,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.6</v>
+        <v>7.614</v>
       </c>
       <c r="N8" t="n">
-        <v>6782</v>
+        <v>6881</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1175,20 +1245,30 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>['Marvel Studios', 'Maximum Effort', '21 Laps Entertainment', '20th Century Studios', 'Kevin Feige Productions', 'TSG Entertainment']</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>https://www.disneylatino.com/peliculas/deadpool-&amp;-wolverine</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Acabaron juntos.</t>
         </is>
@@ -1227,11 +1307,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1623.864</v>
+        <v>11.844</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>/1b2sEjyhc6kqZD4SazdVlVLuIyh.jpg</t>
+          <t>/b1WsCRfomw7tRi12NuseKsAJxYK.jpg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1251,13 +1331,13 @@
         <v>7.153</v>
       </c>
       <c r="N9" t="n">
-        <v>1727</v>
+        <v>1917</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
       </c>
       <c r="P9" t="n">
-        <v>1044396565</v>
+        <v>1056396565</v>
       </c>
       <c r="Q9" t="n">
         <v>99</v>
@@ -1269,16 +1349,26 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures', 'Walt Disney Animation Studios', 'Walt Disney Animation Studios']</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>['English', 'Italiano']</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>['Canada', 'United States of America']</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>El océano los está llamando.</t>
         </is>
@@ -1317,7 +1407,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>140.184</v>
+        <v>4.097</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1338,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.7</v>
+        <v>6.674</v>
       </c>
       <c r="N10" t="n">
-        <v>6255</v>
+        <v>6273</v>
       </c>
       <c r="O10" t="n">
         <v>165000000</v>
@@ -1359,20 +1449,30 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>['Amblin Entertainment', 'Universal Pictures']</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>https://www.universalpictures-latam.com/micro/jurassic-world-dominion</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>La épica conclusión de la era Jurásica.</t>
         </is>
@@ -1411,7 +1511,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>404.22</v>
+        <v>4.572</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1432,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.061</v>
+        <v>7.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2579</v>
+        <v>2626</v>
       </c>
       <c r="O11" t="n">
         <v>100000000</v>
@@ -1453,20 +1553,30 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Illumination']</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>https://www.universalpictures-latam.com/micro/dm4</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="b">
@@ -1501,7 +1611,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>91.89400000000001</v>
+        <v>4.851</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1522,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.268</v>
+        <v>7.265</v>
       </c>
       <c r="N12" t="n">
-        <v>9371</v>
+        <v>9399</v>
       </c>
       <c r="O12" t="n">
         <v>200000000</v>
@@ -1543,16 +1653,26 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>['Marvel Studios', 'Kevin Feige Productions']</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>['广州话 / 廣州話', 'English', 'Español']</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
         <is>
           <t>Entra en una nueva dimensión de Strange.</t>
         </is>
@@ -1591,7 +1711,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>143.079</v>
+        <v>7.05</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1612,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.071</v>
+        <v>8.1</v>
       </c>
       <c r="N13" t="n">
-        <v>9870</v>
+        <v>9941</v>
       </c>
       <c r="O13" t="n">
         <v>100000000</v>
@@ -1633,20 +1753,30 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>['Syncopy', 'Universal Pictures', 'Atlas Entertainment', 'Breakheart Films', 'Peters Creek Entertainment']</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>['Nederlands', 'English']</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>https://www.universalpictures-latam.com/micro/oppenheimer</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Descubre la intensa paradoja del enigmático hombre que debe arriesgarse a destruir el mundo para salvarlo.</t>
         </is>
@@ -1685,7 +1815,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>69.755</v>
+        <v>3.802</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1709,7 +1839,7 @@
         <v>7.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3681</v>
+        <v>3687</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
@@ -1727,16 +1857,26 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Illumination']</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>Prepárate para descubrir la historia jamás contada de un niño de 12 años.</t>
         </is>
@@ -1771,7 +1911,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>13.644</v>
+        <v>3.546</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1795,7 +1935,7 @@
         <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O15" t="n">
         <v>200000000</v>
@@ -1813,16 +1953,26 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>['Bona Film Group', 'Shanghai Film Group', 'DF Pictures', 'Alibaba Pictures Group', 'China Film Group Corporation', 'Distribution Workshop', 'Huaxia Film Distribution', 'Just Creative Studio']</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>['China', 'Hong Kong']</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>['普通话', 'English']</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="b">
@@ -1857,7 +2007,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>101.328</v>
+        <v>3.888</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1878,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="N16" t="n">
-        <v>6686</v>
+        <v>6707</v>
       </c>
       <c r="O16" t="n">
         <v>250000000</v>
@@ -1899,20 +2049,30 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>['Marvel Studios']</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>['English', 'Français', '', 'Español', '']</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>https://disneylatino.com/peliculas/pantera-negra-wakanda-por-siempre</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Por siempre.</t>
         </is>
@@ -1929,7 +2089,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[878, 12, 28]</t>
+          <t>[878, 12, 28, 35]</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1951,7 +2111,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>123.658</v>
+        <v>3.875</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1972,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7.953</v>
+        <v>7.949</v>
       </c>
       <c r="N17" t="n">
-        <v>7162</v>
+        <v>7189</v>
       </c>
       <c r="O17" t="n">
         <v>250000000</v>
@@ -1988,25 +2148,35 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['Ciencia ficción', 'Aventura', 'Acción']</t>
+          <t>['Ciencia ficción', 'Aventura', 'Acción', 'Comedia']</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>['Marvel Studios', 'Kevin Feige Productions']</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>https://www.disneylatino.com/peliculas/guardianes-de-la-galaxia-vol-3</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Listos para el último baile.</t>
         </is>
@@ -2041,7 +2211,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>6.258</v>
+        <v>3.544</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2083,16 +2253,26 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>['Alibaba Pictures Group', 'Tianjin Maoyan Media', 'Beijing Big Bowl Entertainment Culture Media', 'Beijing Culture', 'Beijing Cheering Times Culture &amp; Entertainment', 'Shanghai Ruyi Film &amp; TV Production']</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="b">
@@ -2127,7 +2307,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>41.642</v>
+        <v>4.135</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2151,7 +2331,7 @@
         <v>7.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6408</v>
+        <v>6427</v>
       </c>
       <c r="O19" t="n">
         <v>250000000</v>
@@ -2169,20 +2349,30 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>['GB']</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>['EON Productions', 'Metro-Goldwyn-Mayer']</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>['Español', 'English', 'Italiano', 'Français', 'Pусский']</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>['English', 'Français', 'Italiano', 'Pусский', 'Español']</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>https://www.universalpictures-latam.com/micro/no-time-to-die</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>La misión que cambia todo, comienza...</t>
         </is>
@@ -2221,7 +2411,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>104.7</v>
+        <v>6.013</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2242,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.658</v>
+        <v>7.7</v>
       </c>
       <c r="N20" t="n">
-        <v>10667</v>
+        <v>10721</v>
       </c>
       <c r="O20" t="n">
         <v>185000000</v>
@@ -2263,20 +2453,30 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>['6th &amp; Idaho Motion Picture Company', 'Dylan Clark Productions', 'DC Films', 'Warner Bros. Pictures']</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>https://www.warnerbroslatino.com/es-mx/peliculas/batman</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Desenmascara la verdad.</t>
         </is>
@@ -2315,7 +2515,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>66.104</v>
+        <v>4.095</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2336,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.422</v>
+        <v>6.421</v>
       </c>
       <c r="N21" t="n">
-        <v>7775</v>
+        <v>7789</v>
       </c>
       <c r="O21" t="n">
         <v>250000000</v>
@@ -2357,16 +2557,26 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>['Marvel Studios', 'Kevin Feige Productions']</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
         <is>
           <t>Él no es el único.</t>
         </is>
@@ -2405,7 +2615,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>330.427</v>
+        <v>4.492</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2426,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.901</v>
+        <v>6.907</v>
       </c>
       <c r="N22" t="n">
-        <v>1818</v>
+        <v>1927</v>
       </c>
       <c r="O22" t="n">
         <v>150000000</v>
@@ -2447,20 +2657,30 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Marc Platt Productions']</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>https://www.wickedmovie.com</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Everyone deserves the chance to fly.</t>
         </is>
@@ -2499,7 +2719,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>44.644</v>
+        <v>1.783</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2523,7 +2743,7 @@
         <v>7.1</v>
       </c>
       <c r="N23" t="n">
-        <v>7288</v>
+        <v>7298</v>
       </c>
       <c r="O23" t="n">
         <v>200000000</v>
@@ -2541,20 +2761,30 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>['Original Film', 'One Race', 'Perfect Storm Entertainment', 'Universal Pictures', 'Roth-Kirschenbaum Films']</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>['English', 'Français', 'Deutsch', 'Español']</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>https://www.uphe.com/movies/f9-the-fast-saga</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Not all blood is family.</t>
         </is>
@@ -2593,7 +2823,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>174.334</v>
+        <v>5.664</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2617,7 +2847,7 @@
         <v>8.1</v>
       </c>
       <c r="N24" t="n">
-        <v>6327</v>
+        <v>6418</v>
       </c>
       <c r="O24" t="n">
         <v>190000000</v>
@@ -2635,20 +2865,30 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>['Legendary Pictures']</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>https://www.dunemovie.com</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Long live the fighters.</t>
         </is>
@@ -2665,7 +2905,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[28, 80, 53]</t>
+          <t>[28, 80, 53, 12, 9648]</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2687,7 +2927,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>189.243</v>
+        <v>3.962</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2708,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="N25" t="n">
-        <v>5790</v>
+        <v>5814</v>
       </c>
       <c r="O25" t="n">
         <v>340000000</v>
@@ -2724,25 +2964,35 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['Action', 'Crime', 'Thriller']</t>
+          <t>['Action', 'Crime', 'Thriller', 'Adventure', 'Mystery']</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Original Film', 'One Race', 'Perfect Storm Entertainment']</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>['English', 'Español']</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>https://fastxmovie.com</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>The end of the road begins.</t>
         </is>
@@ -2754,7 +3004,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/cVh8Af7a9JMOJl75ML3Dg2QVEuq.jpg</t>
+          <t>/1w8kutrRucTd3wlYyu5QlUDMiG1.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2777,11 +3027,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>La historia se cuenta en flashbacks y presenta a Mufasa como un cachorro huérfano, perdido y solo hasta que conoce a un simpático león llamado Taka, heredero de un linaje real. Este encuentro casual pone en marcha un viaje de un extraordinario grupo de inadaptados que buscan su destino. Y sus vínculos se pondrán a prueba mientras trabajan juntos para escapar de un enemigo amenazador y letal.</t>
+          <t>Mufasa era un cachorro huérfano, perdido y solo hasta que conoce a un simpático león llamado Taka, heredero de un linaje real. Este encuentro casual pone en marcha un viaje de un extraordinario grupo de inadaptados que buscan su destino.</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2049.75</v>
+        <v>10.95</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2802,10 +3052,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7.5</v>
+        <v>7.469</v>
       </c>
       <c r="N26" t="n">
-        <v>1446</v>
+        <v>1652</v>
       </c>
       <c r="O26" t="n">
         <v>200000000</v>
@@ -2823,20 +3073,30 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures']</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>https://movies.disney.com/mufasa-the-lion-king</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>The story of an orphan who would be king.</t>
         </is>
@@ -2875,7 +3135,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>145.068</v>
+        <v>4.741</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2899,7 +3159,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>7342</v>
+        <v>7383</v>
       </c>
       <c r="O27" t="n">
         <v>100000000</v>
@@ -2917,20 +3177,30 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>['Columbia Pictures', 'Sony Pictures Animation', 'Lord Miller', 'Pascal Pictures', 'Arad Productions', 'Marvel Entertainment']</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>['English', 'हिन्दी', 'Italiano', 'Español']</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>https://www.sonypictures.com/movies/spidermanacrossthespiderverse</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>It's how you wear the mask that matters.</t>
         </is>
@@ -2965,7 +3235,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>11.885</v>
+        <v>3.014</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3007,16 +3277,26 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>['Beijing Yitong Legend Films', 'China Film Co-Production Corp.', 'As One Production', 'Wanda Pictures']</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>['日本語', '普通话']</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="b">
@@ -3051,7 +3331,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8.147</v>
+        <v>3.558</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3072,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.901</v>
+        <v>5.9</v>
       </c>
       <c r="N29" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3093,16 +3373,26 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>['Huanxi Media Group', 'Edko Films', 'Emperor Motion Pictures']</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>['China', 'Hong Kong']</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="b">
@@ -3137,7 +3427,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>73.376</v>
+        <v>3.704</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3158,10 +3448,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7.095</v>
+        <v>7.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3769</v>
+        <v>3795</v>
       </c>
       <c r="O30" t="n">
         <v>125000000</v>
@@ -3179,20 +3469,30 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>['GB']</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Village Roadshow Pictures', 'The Roald Dahl Story Company', 'Heyday Films', 'Domain Entertainment']</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>https://www.wonkamovie.com</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Every good thing in this world started with a dream.</t>
         </is>
@@ -3231,7 +3531,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>13.956</v>
+        <v>2.596</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3255,7 +3555,7 @@
         <v>6.2</v>
       </c>
       <c r="N31" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O31" t="n">
         <v>200000000</v>
@@ -3273,16 +3573,26 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>['Bona Film Group', 'Distribution Workshop', 'China Film Group Corporation', 'Alibaba Pictures Group', 'Huaxia Film Distribution', 'Just Creative Studio', 'Mandrill Visual Effects']</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>['China', 'Hong Kong']</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>['English', '普通话']</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="b">
@@ -3317,7 +3627,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.251</v>
+        <v>3.845</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3338,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>7.3</v>
+        <v>7.278</v>
       </c>
       <c r="N32" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="O32" t="n">
         <v>73800000</v>
@@ -3359,20 +3669,30 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>['China Film Group Corporation', 'Guo Fan Culture and Media']</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>['普通话', 'English', 'Français', '日本語', 'Português', 'Pусский', 'Español']</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>https://trinitycineasia.com/in-cinemas/the-wandering-earth-ii/</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="b">
@@ -3407,7 +3727,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>149.531</v>
+        <v>3.962</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3431,7 +3751,7 @@
         <v>7.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4073</v>
+        <v>4094</v>
       </c>
       <c r="O33" t="n">
         <v>150000000</v>
@@ -3449,20 +3769,30 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>['Legendary Pictures']</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>https://www.godzillaxkongmovie.com</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Rise together or fall alone.</t>
         </is>
@@ -3501,7 +3831,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>78.751</v>
+        <v>3.609</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3522,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6.3</v>
+        <v>6.317</v>
       </c>
       <c r="N34" t="n">
-        <v>3000</v>
+        <v>3015</v>
       </c>
       <c r="O34" t="n">
         <v>297000000</v>
@@ -3543,20 +3873,30 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures', 'Lucamar Productions', 'Marc Platt Productions']</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>https://movies.disney.com/the-little-mermaid-2023</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Watch and you'll see, some day I'll be, part of your world!</t>
         </is>
@@ -3595,7 +3935,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>92.709</v>
+        <v>4.944</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3619,7 +3959,7 @@
         <v>7.531</v>
       </c>
       <c r="N35" t="n">
-        <v>4052</v>
+        <v>4080</v>
       </c>
       <c r="O35" t="n">
         <v>291000000</v>
@@ -3637,20 +3977,30 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>['Paramount Pictures', 'Skydance Media', 'TC Productions']</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
         <is>
           <t>['Français', 'English', 'Italiano', 'Pусский']</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>https://www.paramountmovies.com/movies/mission-impossible-dead-reckoning</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>We all share the same fate.</t>
         </is>
@@ -3667,7 +4017,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[16, 10751, 28, 35]</t>
+          <t>[16, 10751, 28, 35, 12, 14]</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3689,7 +4039,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>170.597</v>
+        <v>3.891</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3710,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>7.073</v>
+        <v>7.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2986</v>
+        <v>2998</v>
       </c>
       <c r="O36" t="n">
         <v>80000000</v>
@@ -3726,25 +4076,39 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>['Animation', 'Family', 'Action', 'Comedy']</t>
+          <t>['Animation', 'Family', 'Action', 'Comedy', 'Adventure', 'Fantasy']</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>['DreamWorks Animation']</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>https://www.dreamworks.com/movies/kung-fu-panda-4</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Quadruple the awesomeness.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="b">
@@ -3779,7 +4143,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>62.606</v>
+        <v>4.422</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3803,7 +4167,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>4018</v>
+        <v>4034</v>
       </c>
       <c r="O37" t="n">
         <v>15700000</v>
@@ -3821,20 +4185,30 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>['JP']</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>['ufotable', 'Aniplex', 'Shueisha', 'TOHO']</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>['Japan']</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
         <is>
           <t>['日本語']</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>https://demonslayer-anime.com</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>With your blade, bring an end to the nightmare.</t>
         </is>
@@ -3873,7 +4247,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>74.563</v>
+        <v>5.67</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3894,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6.8</v>
+        <v>6.777</v>
       </c>
       <c r="N38" t="n">
-        <v>10516</v>
+        <v>10548</v>
       </c>
       <c r="O38" t="n">
         <v>110000000</v>
@@ -3915,20 +4289,30 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>['Columbia Pictures', 'Pascal Pictures', 'Matt Tolmach Productions', 'Arad Productions']</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
         <is>
           <t>['Español', 'English']</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>https://www.venom.movie</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>It’s time to meet Carnage.</t>
         </is>
@@ -3967,7 +4351,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12.63</v>
+        <v>2.804</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3988,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6.1</v>
+        <v>6.199</v>
       </c>
       <c r="N39" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O39" t="n">
         <v>239000000</v>
@@ -4009,16 +4393,26 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
+          <t>['IN']</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>['Red Chillies Entertainment', 'Rajkumar Hirani Films', 'Jio Studios']</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>['India']</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
         <is>
           <t>['हिन्दी', 'ਪੰਜਾਬੀ']</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
         <is>
           <t>A Soldier's journey to keep a promise</t>
         </is>
@@ -4057,7 +4451,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>104.218</v>
+        <v>4.381</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4078,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>7.6</v>
+        <v>7.618</v>
       </c>
       <c r="N40" t="n">
-        <v>4684</v>
+        <v>4711</v>
       </c>
       <c r="O40" t="n">
         <v>200000000</v>
@@ -4099,20 +4493,30 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures', 'Pixar']</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>https://movies.disney.com/elemental</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Opposites react.</t>
         </is>
@@ -4124,16 +4528,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/jr8tSoJGj33XLgFBy6lmZhpGQNu.jpg</t>
+          <t>/zOpe0eHsq0A2NvNyBbtT6sj53qV.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[16, 12, 14, 35, 10751]</t>
+          <t>[28, 878, 35, 10751, 12, 14]</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>315162</v>
+        <v>939243</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4142,73 +4546,83 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puss in Boots: The Last Wish</t>
+          <t>Sonic the Hedgehog 3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>El audaz forajido Gato con Botas descubre que su pasión por el peligro y su desprecio por la seguridad le han pasado factura. El Gato ha quemado ocho de sus nueve vidas, aunque ha perdido la cuenta por el camino. Recuperar esas vidas hará que el Gato con Botas emprenda su mayor búsqueda hasta ahora; la mítica Estrella de los Deseos.</t>
+          <t>Sonic, Knuckles y Tails se reúnen para enfrentarse a un nuevo y poderoso adversario, Shadow, un misterioso villano con poderes nunca antes vistos. Con sus habilidades superadas en todos los sentidos, el Equipo Sonic debe buscar una alianza improbable con la esperanza de detener a Shadow y proteger el planeta.</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>127.8</v>
+        <v>10.217</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>/b5Jb7GoQaqIXy4VEdnQa0UrQZI.jpg</t>
+          <t>/3aDWCRXLYOCuxjrjiPfLd79tcI6.jpg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Gato con Botas: El último deseo</t>
+          <t>Sonic 3: La Película</t>
         </is>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.721</v>
       </c>
       <c r="N41" t="n">
-        <v>8025</v>
+        <v>2188</v>
       </c>
       <c r="O41" t="n">
-        <v>90000000</v>
+        <v>122000000</v>
       </c>
       <c r="P41" t="n">
-        <v>484700000</v>
+        <v>486018457</v>
       </c>
       <c r="Q41" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>['Animation', 'Adventure', 'Fantasy', 'Comedy', 'Family']</t>
+          <t>['Action', 'Science Fiction', 'Comedy', 'Family', 'Adventure', 'Fantasy']</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>['DreamWorks Animation']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>['English', 'Español']</t>
+          <t>['Paramount Pictures', 'Original Film', 'Marza Animation Planet', 'SEGA', 'Blur Studio', 'SEGA of America']</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://www.dreamworks.com/movies/puss-in-boots-the-last-wish</t>
+          <t>['United States of America', 'Japan']</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Every legend comes to an end.</t>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>https://www.sonicthehedgehogmovie.com</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>New adventure. New rival.</t>
         </is>
       </c>
     </row>
@@ -4218,87 +4632,101 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/9IEYCg2Sxk72QdNNcvbbCMelalu.jpg</t>
+          <t>/jr8tSoJGj33XLgFBy6lmZhpGQNu.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[18, 35, 28]</t>
+          <t>[16, 12, 14, 35, 10751]</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1229349</v>
+        <v>315162</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>热辣滚烫</t>
+          <t>Puss in Boots: The Last Wish</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hace años que Le Ying (interpretada por Jia Ling) vive en casa de sus padres, sin dirección en la vida y sin hacer nada en particular. Después de graduarse de la universidad y trabajar solo por un tiempo, Le Ying decide aislarse de la sociedad. Un día, después de varias vueltas del destino, decide vivir la vida de otra manera. Al aventurarse con cautela en el mundo exterior, Le Ying conoce al entrenador de boxeo Hao Kun (Lei Jia Yin). Justo cuando cree que la vida está a punto de dar un giro positivo, los desafíos que debe enfrentar superan ampliamente lo que había imaginado, y su vibrante vida acaba de comenzar…</t>
+          <t>El audaz forajido Gato con Botas descubre que su pasión por el peligro y su desprecio por la seguridad le han pasado factura. El Gato ha quemado ocho de sus nueve vidas, aunque ha perdido la cuenta por el camino. Recuperar esas vidas hará que el Gato con Botas emprenda su mayor búsqueda hasta ahora; la mítica Estrella de los Deseos.</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.308</v>
+        <v>4.471</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>/3JJSLb9nQutbMRY9lwpMVoKEBhm.jpg</t>
+          <t>/b5Jb7GoQaqIXy4VEdnQa0UrQZI.jpg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Yolo - solo se vive una vez</t>
+          <t>Gato con Botas: El último deseo</t>
         </is>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>74</v>
+        <v>8052</v>
       </c>
       <c r="O42" t="n">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="P42" t="n">
-        <v>480600000</v>
+        <v>484700000</v>
       </c>
       <c r="Q42" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>['Drama', 'Comedy', 'Action']</t>
+          <t>['Animation', 'Adventure', 'Fantasy', 'Comedy', 'Family']</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>['Alibaba Pictures Group', 'Beijing Big Bowl Entertainment Culture Media', 'China Film Group Corporation', 'New Classics Media', 'Tencent Penguin Pictures']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>['普通话']</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr"/>
+          <t>['DreamWorks Animation']</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>To win, at least once.</t>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>https://www.dreamworks.com/movies/puss-in-boots-the-last-wish</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Say hola to his little friends.</t>
         </is>
       </c>
     </row>
@@ -4308,91 +4736,97 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/vZG7PrX9HmdgL5qfZRjhJsFYEIA.jpg</t>
+          <t>/9IEYCg2Sxk72QdNNcvbbCMelalu.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[28, 878, 12]</t>
+          <t>[18, 35, 28]</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>912649</v>
+        <v>1229349</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Venom: The Last Dance</t>
+          <t>热辣滚烫</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Eddie y Venom están huyendo. Perseguidos por sus dos mundos, el dúo se ve obligado a tomar una decisión devastadora que bajará el telón en un último baile entre Venom y Eddie.</t>
+          <t>Hace años que Le Ying (interpretada por Jia Ling) vive en casa de sus padres, sin dirección en la vida y sin hacer nada en particular. Después de graduarse de la universidad y trabajar solo por un tiempo, Le Ying decide aislarse de la sociedad. Un día, después de varias vueltas del destino, decide vivir la vida de otra manera. Al aventurarse con cautela en el mundo exterior, Le Ying conoce al entrenador de boxeo Hao Kun (Lei Jia Yin). Justo cuando cree que la vida está a punto de dar un giro positivo, los desafíos que debe enfrentar superan ampliamente lo que había imaginado, y su vibrante vida acaba de comenzar…</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>701.816</v>
+        <v>2.705</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>/8F74DwgFxTIBNtbqSLjR7zWmnHh.jpg</t>
+          <t>/3JJSLb9nQutbMRY9lwpMVoKEBhm.jpg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Venom: El último baile</t>
+          <t>Yolo - solo se vive una vez</t>
         </is>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.783</v>
+        <v>6.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2915</v>
+        <v>75</v>
       </c>
       <c r="O43" t="n">
-        <v>120000000</v>
+        <v>100000000</v>
       </c>
       <c r="P43" t="n">
-        <v>478103649</v>
+        <v>480600000</v>
       </c>
       <c r="Q43" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>['Action', 'Science Fiction', 'Adventure']</t>
+          <t>['Drama', 'Comedy', 'Action']</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>['Columbia Pictures', 'Pascal Pictures', 'Matt Tolmach Productions', 'Hutch Parker Entertainment', 'Arad Productions']</t>
+          <t>['CN']</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>['English']</t>
+          <t>['Alibaba Pictures Group', 'Beijing Big Bowl Entertainment Culture Media', 'China Film Group Corporation', 'New Classics Media', 'Tencent Penguin Pictures', 'Taurus Film']</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://venom.movie</t>
+          <t>['China']</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>'Til death do they part.</t>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>To win, at least once.</t>
         </is>
       </c>
     </row>
@@ -4402,16 +4836,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/m8JTwHFwX7I7JY5fPe4SjqejWag.jpg</t>
+          <t>/vZG7PrX9HmdgL5qfZRjhJsFYEIA.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[28, 12, 878]</t>
+          <t>[28, 878, 12]</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>640146</v>
+        <v>912649</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4420,73 +4854,83 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ant-Man and the Wasp: Quantumania</t>
+          <t>Venom: The Last Dance</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Los superhéroes Scott Lang y Hope van Dyne regresan para continuar sus aventuras como Ant-Man y Wasp. Con los padres de Hope, Hank Pym y Janet van Dyne, y con la hija de Scott, Cassie Lang, la familia explora el Reino Quántico, interactúa con extrañas criaturas y se embarca en una aventura que los hará ir más allá de lo que creían posible.</t>
+          <t>Eddie y Venom están huyendo. Perseguidos por sus dos mundos, el dúo se ve obligado a tomar una decisión devastadora que bajará el telón en un último baile entre Venom y Eddie.</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>44.142</v>
+        <v>5.662</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>/lKHy0ntGPdQeFwvNq8gK1D0anEr.jpg</t>
+          <t>/8F74DwgFxTIBNtbqSLjR7zWmnHh.jpg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ant-Man and the Wasp: Quantumania</t>
+          <t>Venom: El último baile</t>
         </is>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.298</v>
+        <v>6.796</v>
       </c>
       <c r="N44" t="n">
-        <v>5158</v>
+        <v>3029</v>
       </c>
       <c r="O44" t="n">
-        <v>388369742</v>
+        <v>120000000</v>
       </c>
       <c r="P44" t="n">
-        <v>476071180</v>
+        <v>478103649</v>
       </c>
       <c r="Q44" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>['Action', 'Adventure', 'Science Fiction']</t>
+          <t>['Action', 'Science Fiction', 'Adventure']</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>['Columbia Pictures', 'Pascal Pictures', 'Matt Tolmach Productions', 'Hutch Parker Entertainment', 'Arad Productions']</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>https://www.marvel.com/movies/ant-man-and-the-wasp-quantumania</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Witness the beginning of a new dynasty.</t>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>https://venom.movie</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>'Til death do they part.</t>
         </is>
       </c>
     </row>
@@ -4496,81 +4940,103 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/vH0IXldpTM8J3MCT35khoeUMb5E.jpg</t>
+          <t>/m8JTwHFwX7I7JY5fPe4SjqejWag.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[28, 12, 878]</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1299537</v>
+        <v>640146</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Ant-Man and the Wasp: Quantumania</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Los superhéroes Scott Lang y Hope van Dyne regresan para continuar sus aventuras como Ant-Man y Wasp. Con los padres de Hope, Hank Pym y Janet van Dyne, y con la hija de Scott, Cassie Lang, la familia explora el Reino Quántico, interactúa con extrañas criaturas y se embarca en una aventura que los hará ir más allá de lo que creían posible.</t>
+        </is>
+      </c>
       <c r="H45" t="n">
-        <v>12.562</v>
+        <v>4.157</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>/dFNJOjtKD9ypSHciXY6JRgK24Pw.jpg</t>
+          <t>/lKHy0ntGPdQeFwvNq8gK1D0anEr.jpg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>抓娃娃</t>
+          <t>Ant-Man and the Wasp: Quantumania</t>
         </is>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="N45" t="n">
-        <v>53</v>
+        <v>5178</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>388369742</v>
       </c>
       <c r="P45" t="n">
-        <v>473859800</v>
+        <v>476071180</v>
       </c>
       <c r="Q45" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>['Comedy']</t>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>['海口西虹胡同影视文化有限公司', 'Tianjin Maoyan Weiying Culture Media', 'Fun Age Pictures', 'Shanghai Ruyi Film &amp; TV Production', 'Alibaba Pictures Group', 'Horgos Coloroom Pictures', 'China Film Group Corporation', '长影时代传媒股份有限公司', '西虹市影视文化', 'New Classics Media', '海南乐镜影视文化传媒有限公司', 'Zhejiang Hengdian Film Production', 'Tencent Penguin Pictures', '蜃景影视文化传播（海口）有限公司', '安徽文逸影视文化传媒有限公司', '吉林省石头剪刀布传媒有限公司', 'Wanda Pictures', 'Youku']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>['普通话']</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/ant-man-and-the-wasp-quantumania</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Witness the beginning of a new dynasty.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="b">
@@ -4578,93 +5044,91 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/zOpe0eHsq0A2NvNyBbtT6sj53qV.jpg</t>
+          <t>/vH0IXldpTM8J3MCT35khoeUMb5E.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[28, 878, 35, 10751]</t>
+          <t>[35]</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>939243</v>
+        <v>1299537</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog 3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Sonic, Knuckles y Tails se reúnen para enfrentarse a un nuevo y poderoso adversario, Shadow, un misterioso villano con poderes nunca antes vistos. Con sus habilidades superadas en todos los sentidos, el Equipo Sonic debe buscar una alianza improbable con la esperanza de detener a Shadow y proteger el planeta.</t>
-        </is>
-      </c>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1866.273</v>
+        <v>2.036</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>/3aDWCRXLYOCuxjrjiPfLd79tcI6.jpg</t>
+          <t>/dFNJOjtKD9ypSHciXY6JRgK24Pw.jpg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Sonic 3: La Película</t>
+          <t>抓娃娃</t>
         </is>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>7.752</v>
+        <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>2011</v>
+        <v>55</v>
       </c>
       <c r="O46" t="n">
-        <v>122000000</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>472518457</v>
+        <v>473859800</v>
       </c>
       <c r="Q46" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>['Action', 'Science Fiction', 'Comedy', 'Family']</t>
+          <t>['Comedy']</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>['Paramount Pictures', 'Original Film', 'Marza Animation Planet', 'SEGA', 'Blur Studio', 'SEGA of America']</t>
+          <t>['CN']</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>['English']</t>
+          <t>['海口西虹胡同影视文化有限公司', 'Tianjin Maoyan Weiying Culture Media', 'Fun Age Pictures', 'Shanghai Ruyi Film &amp; TV Production', 'Alibaba Pictures Group', 'Horgos Coloroom Pictures', 'China Film Group Corporation', '长影时代传媒股份有限公司', '西虹市影视文化', 'New Classics Media', '海南乐镜影视文化传媒有限公司', 'Zhejiang Hengdian Film Production', 'Tencent Penguin Pictures', '蜃景影视文化传播（海口）有限公司', '安徽文逸影视文化传媒有限公司', '吉林省石头剪刀布传媒有限公司', 'Wanda Pictures', 'Youku']</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://www.sonicthehedgehogmovie.com</t>
+          <t>['China']</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>New adventure. New rival.</t>
-        </is>
-      </c>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="b">
@@ -4699,7 +5163,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>43.742</v>
+        <v>4.082</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4720,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.6</v>
+        <v>7.582</v>
       </c>
       <c r="N47" t="n">
-        <v>10096</v>
+        <v>10113</v>
       </c>
       <c r="O47" t="n">
         <v>200000000</v>
@@ -4741,20 +5205,30 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>['Legendary Pictures']</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>https://www.warnerbros.com/movies/godzilla-vs-kong</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>One will fall.</t>
         </is>
@@ -4789,7 +5263,7 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>7.824</v>
+        <v>2.07</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4810,10 +5284,10 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>7.2</v>
+        <v>7.246</v>
       </c>
       <c r="N48" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -4831,16 +5305,26 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>['Shanghai PMF Media', 'Tao Piao Piao', 'Maoyan Entertainment', 'Bona Film Group', 'China Film Group Corporation', 'Fun Age Pictures', 'Zhejiang Hengdian Film Production', 'Shanghai Ruyi Film &amp; TV Production', '上海电影（集团）有限公司', 'Weibo Corporation']</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="b">
@@ -4875,7 +5359,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>15.13</v>
+        <v>3.792</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4899,7 +5383,7 @@
         <v>6.9</v>
       </c>
       <c r="N49" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O49" t="n">
         <v>80000000</v>
@@ -4917,20 +5401,30 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>['Beijing Diqi Yinxiang Entertainment', 'Huayi Brothers Pictures', 'Beijing Enlight Pictures', 'Tencent Pictures', 'South Australian Film Corporation', 'Huaxia Film Distribution']</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
         <is>
           <t>['普通话', 'English', '日本語']</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>https://cmc-pictures.com/the-eight-hundred/</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>Based on the true story of one of the greatest battles of WWII.</t>
         </is>
@@ -4965,7 +5459,7 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>6.302</v>
+        <v>3.023</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4986,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6.882</v>
+        <v>6.9</v>
       </c>
       <c r="N50" t="n">
         <v>85</v>
@@ -5007,16 +5501,26 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>['Fun Age Pictures']</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="b">
@@ -5024,7 +5528,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/bHeUgZKqduubnNl8GshjrpHS9lF.jpg</t>
+          <t>/8mjYwWT50GkRrrRdyHzJorfEfcl.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5051,7 +5555,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>616.14</v>
+        <v>6.648</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5060,7 +5564,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5072,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>6.8</v>
+        <v>6.774</v>
       </c>
       <c r="N51" t="n">
-        <v>2920</v>
+        <v>3033</v>
       </c>
       <c r="O51" t="n">
         <v>310000000</v>
@@ -5084,7 +5588,7 @@
         <v>458718000</v>
       </c>
       <c r="Q51" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5093,20 +5597,30 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>['Paramount Pictures', 'Scott Free Productions', 'Lucy Fisher/Douglas Wick Productions']</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>https://www.gladiator.movie</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>Prepare to be entertained.</t>
         </is>
@@ -5118,7 +5632,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/xi1VSt3DtkevUmzCx2mNlCoDe74.jpg</t>
+          <t>/vchI0KSlYgCInkAdBlDaxL9xhq5.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5145,7 +5659,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>84.188</v>
+        <v>4.748</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5166,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7.067</v>
+        <v>7.045</v>
       </c>
       <c r="N52" t="n">
-        <v>2336</v>
+        <v>2379</v>
       </c>
       <c r="O52" t="n">
         <v>100000000</v>
@@ -5187,20 +5701,30 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Geffen Pictures', 'Plan B Entertainment', 'Tim Burton Productions', 'Tommy Harper Productions', 'Domain Entertainment']</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>https://www.beetlejuicemovie.com</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>The ghost with the most is back.</t>
         </is>
@@ -5239,7 +5763,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>141.19</v>
+        <v>3.819</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5260,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.25</v>
+        <v>7.248</v>
       </c>
       <c r="N53" t="n">
-        <v>4814</v>
+        <v>4834</v>
       </c>
       <c r="O53" t="n">
         <v>195000000</v>
@@ -5281,20 +5805,30 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>['Skydance Media', 'Paramount Pictures', 'di Bonaventura Pictures', 'Bay Films', 'New Republic Pictures', 'DeSanto/Murphy Productions', 'Hasbro']</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
         <is>
           <t>['', 'Español', 'English']</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>https://www.paramountmovies.com/movies/transformers-rise-of-the-beasts</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Unite or fall.</t>
         </is>
@@ -5333,7 +5867,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>127.893</v>
+        <v>4.445</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5354,10 +5888,10 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>7.721</v>
+        <v>7.7</v>
       </c>
       <c r="N54" t="n">
-        <v>6870</v>
+        <v>6896</v>
       </c>
       <c r="O54" t="n">
         <v>90000000</v>
@@ -5375,20 +5909,30 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>['Thunder Road', '87Eleven', 'Studio Babelsberg', 'Lionsgate']</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>['Germany', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
         <is>
           <t>['العربية', '广州话 / 廣州話', 'English', 'Français', 'Deutsch', '日本語', 'Latin', 'Pусский', 'Español']</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>https://johnwick.movie/film/john-wick-4</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>No way back, one way out.</t>
         </is>
@@ -5427,7 +5971,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>77.93000000000001</v>
+        <v>3.679</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5448,10 +5992,10 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>6.617</v>
+        <v>6.6</v>
       </c>
       <c r="N55" t="n">
-        <v>2977</v>
+        <v>2992</v>
       </c>
       <c r="O55" t="n">
         <v>205000000</v>
@@ -5469,20 +6013,30 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'The Safran Company', 'Atomic Monster', 'DC Films', 'Domain Entertainment']</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>['한국어/조선말', '普通话', 'English']</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>['English', '普通话', '한국어/조선말']</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>https://www.aquamanmovie.com</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>The tide is turning.</t>
         </is>
@@ -5521,7 +6075,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>71.59699999999999</v>
+        <v>4.156</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5542,10 +6096,10 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>7.528</v>
+        <v>7.526</v>
       </c>
       <c r="N56" t="n">
-        <v>9577</v>
+        <v>9600</v>
       </c>
       <c r="O56" t="n">
         <v>150000000</v>
@@ -5563,20 +6117,30 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
           <t>['Marvel Studios']</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
         <is>
           <t>['English', '普通话']</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>https://www.marvel.com/movies/shang-chi-and-the-legend-of-the-ten-rings</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>You can't outrun your destiny.</t>
         </is>
@@ -5611,7 +6175,7 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.273</v>
+        <v>0.047</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5653,20 +6217,30 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>https://www.metallica.com/events/2019-06-18-manchester-england.html</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="b">
@@ -5701,7 +6275,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>62.972</v>
+        <v>4.622</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5725,7 +6299,7 @@
         <v>7.135</v>
       </c>
       <c r="N58" t="n">
-        <v>8352</v>
+        <v>8363</v>
       </c>
       <c r="O58" t="n">
         <v>90000000</v>
@@ -5743,20 +6317,30 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
           <t>['Columbia Pictures', '2.0 Entertainment', 'Don Simpson/Jerry Bruckheimer Films', 'Overbrook Entertainment']</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
         <is>
           <t>['English', 'Español']</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>https://www.sonypictures.com/movies/badboysforlife</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Ride together. Die together.</t>
         </is>
@@ -5795,7 +6379,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>73.711</v>
+        <v>4.086</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5816,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.853</v>
+        <v>7.9</v>
       </c>
       <c r="N59" t="n">
-        <v>4460</v>
+        <v>4469</v>
       </c>
       <c r="O59" t="n">
         <v>85000000</v>
@@ -5828,7 +6412,7 @@
         <v>408402685</v>
       </c>
       <c r="Q59" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -5837,20 +6421,30 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Illumination']</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>https://www.illumination.com/movie/sing-2/</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Where will your dreams take you?</t>
         </is>
@@ -5889,7 +6483,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>118.972</v>
+        <v>6.354</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5910,10 +6504,10 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>7.8</v>
+        <v>7.782</v>
       </c>
       <c r="N60" t="n">
-        <v>13227</v>
+        <v>13304</v>
       </c>
       <c r="O60" t="n">
         <v>165000000</v>
@@ -5931,20 +6525,30 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>['Legendary Pictures']</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
         <is>
           <t>['普通话', 'English']</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>https://www.dunemovie.com/</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>It begins.</t>
         </is>
@@ -5983,7 +6587,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>48.423</v>
+        <v>3.867</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6007,7 +6611,7 @@
         <v>6.647</v>
       </c>
       <c r="N61" t="n">
-        <v>4611</v>
+        <v>4627</v>
       </c>
       <c r="O61" t="n">
         <v>200000000</v>
@@ -6025,20 +6629,30 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
+          <t>['US', 'GB']</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Heyday Films']</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>https://www.fantasticbeasts.com</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Return to the magic.</t>
         </is>
@@ -6077,7 +6691,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>96.09699999999999</v>
+        <v>4.402</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6098,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6.918</v>
+        <v>6.916</v>
       </c>
       <c r="N62" t="n">
-        <v>6140</v>
+        <v>6165</v>
       </c>
       <c r="O62" t="n">
         <v>120000000</v>
@@ -6119,20 +6733,30 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
           <t>['Columbia Pictures', 'Atlas Entertainment', 'PlayStation Productions', 'Arad Productions']</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
         <is>
           <t>['English', 'Español']</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>https://www.unchartedmovie.com</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Fortune favors the bold.</t>
         </is>
@@ -6171,7 +6795,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>165.078</v>
+        <v>3.855</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6192,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>7.48</v>
+        <v>7.474</v>
       </c>
       <c r="N63" t="n">
-        <v>5361</v>
+        <v>5394</v>
       </c>
       <c r="O63" t="n">
         <v>110000000</v>
@@ -6213,20 +6837,30 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
           <t>['Original Film', 'Blur Studio', 'Marza Animation Planet', 'Paramount Pictures', 'SEGA', 'SEGA of America']</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>['Japan', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>https://www.paramountmovies.com/movies/sonic-the-hedgehog-2</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Welcome to the next level.</t>
         </is>
@@ -6265,7 +6899,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>222.002</v>
+        <v>4.226</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6286,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>7.386</v>
+        <v>7.383</v>
       </c>
       <c r="N64" t="n">
-        <v>2776</v>
+        <v>2795</v>
       </c>
       <c r="O64" t="n">
         <v>100000000</v>
@@ -6307,20 +6941,30 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
           <t>['Westbrook', 'Columbia Pictures', 'Don Simpson/Jerry Bruckheimer Films', '2.0 Entertainment']</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>https://www.badboys.movie</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Miami's finest are now its most wanted.</t>
         </is>
@@ -6332,7 +6976,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>/c6H7Z4u73ir3cIoCteuhJh7UCAR.jpg</t>
+          <t>/oaLl6puFpgisUF3bXT5h0g29d07.jpg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6359,7 +7003,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>53.862</v>
+        <v>4.858</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6383,7 +7027,7 @@
         <v>6.8</v>
       </c>
       <c r="N65" t="n">
-        <v>8428</v>
+        <v>8453</v>
       </c>
       <c r="O65" t="n">
         <v>200000000</v>
@@ -6401,20 +7045,30 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
           <t>['Marvel Studios']</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
         <is>
           <t>['العربية', 'English', 'हिन्दी', 'Latin', 'Español']</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>https://www.marvel.com/movies/eternals</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>In the beginning...</t>
         </is>
@@ -6487,16 +7141,26 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
         <is>
           <t>THE MOST FOLLOWED ARGENTINE IN THE WORLD SOLD OUT 11 PERFORMANCES AT THE GRAN REX, MAKING HISTORY FOR THE COUNTRY.</t>
         </is>
@@ -6513,7 +7177,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[878, 12, 28]</t>
+          <t>[878, 12, 28, 18, 53]</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -6535,7 +7199,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>146.974</v>
+        <v>3.919</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6556,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>7.1</v>
+        <v>7.083</v>
       </c>
       <c r="N67" t="n">
-        <v>3583</v>
+        <v>3617</v>
       </c>
       <c r="O67" t="n">
         <v>160000000</v>
@@ -6572,25 +7236,35 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>['Science Fiction', 'Adventure', 'Action']</t>
+          <t>['Science Fiction', 'Adventure', 'Action', 'Drama', 'Thriller']</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
           <t>['20th Century Studios', 'Oddball Entertainment', 'Jason T. Reed Productions']</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>https://www.20thcenturystudios.com/movies/kingdom-of-the-planet-of-the-apes</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>No one can stop the reign.</t>
         </is>
@@ -6629,7 +7303,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>53.191</v>
+        <v>4.074</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6650,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>6.88</v>
+        <v>6.9</v>
       </c>
       <c r="N68" t="n">
-        <v>6443</v>
+        <v>6461</v>
       </c>
       <c r="O68" t="n">
         <v>200000000</v>
@@ -6671,20 +7345,30 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
           <t>['New Line Cinema', 'Flynn Picture Company', 'DC Films', 'Seven Bucks Productions', 'Warner Bros. Pictures']</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>https://www.dc.com/BlackAdam</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>The world needed a hero. It got Black Adam.</t>
         </is>
@@ -6719,7 +7403,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>3.795</v>
+        <v>1.431</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6761,20 +7445,30 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
           <t>['New Classics Media', 'Slinky Town Pictures', 'Tianjin Yuewen Media']</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>https://www.wellgousa.com/films/too-cool-to-kill</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="b">
@@ -6809,7 +7503,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>73.271</v>
+        <v>3.606</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6830,10 +7524,10 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>6.5</v>
+        <v>6.449</v>
       </c>
       <c r="N70" t="n">
-        <v>3520</v>
+        <v>3534</v>
       </c>
       <c r="O70" t="n">
         <v>129000000</v>
@@ -6851,20 +7545,30 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
           <t>['Apelles Entertainment', 'Warner Bros. Pictures', 'di Bonaventura Pictures', 'CMC Pictures', 'Onaroll Productions', 'DF Pictures']</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>['China', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>https://www.themeg.movie</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Back for seconds.</t>
         </is>
@@ -6903,7 +7607,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>67.693</v>
+        <v>4.655</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6924,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6.561</v>
+        <v>6.6</v>
       </c>
       <c r="N71" t="n">
-        <v>3560</v>
+        <v>3579</v>
       </c>
       <c r="O71" t="n">
         <v>294700000</v>
@@ -6945,20 +7649,30 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
           <t>['Lucasfilm Ltd.']</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
         <is>
           <t>['English', 'العربية', 'Español', 'Deutsch', 'Français']</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>https://movies.disney.com/indiana-jones-and-the-dial-of-destiny</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>His final adventure will be his greatest.</t>
         </is>
@@ -6997,7 +7711,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>57.154</v>
+        <v>4.137</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7018,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7.2</v>
+        <v>7.212</v>
       </c>
       <c r="N72" t="n">
-        <v>10363</v>
+        <v>10384</v>
       </c>
       <c r="O72" t="n">
         <v>200000000</v>
@@ -7039,20 +7753,30 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
           <t>['Marvel Studios']</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
         <is>
           <t>['English', 'Pусский']</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>https://www.marvel.com/movies/black-widow</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>Her world. Her secrets. Her legacy.</t>
         </is>
@@ -7091,7 +7815,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>88.16</v>
+        <v>4.35</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7112,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>6.9</v>
+        <v>6.857</v>
       </c>
       <c r="N73" t="n">
-        <v>2244</v>
+        <v>2293</v>
       </c>
       <c r="O73" t="n">
         <v>155000000</v>
@@ -7133,20 +7857,30 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Warner Bros. Pictures', 'Amblin Entertainment', 'Domain Entertainment']</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>https://www.twisters-movie.com</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Chase. Ride. Survive.</t>
         </is>
@@ -7185,7 +7919,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>58.346</v>
+        <v>3.817</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -7206,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>7.075</v>
+        <v>7.085</v>
       </c>
       <c r="N74" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="O74" t="n">
         <v>85000000</v>
@@ -7227,16 +7961,26 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>['Beijing Culture', 'Century Changshengtian Film', 'Tencent Penguin Pictures', 'Maoyan Entertainment', 'Huaxia Film Distribution']</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="b">
@@ -7271,7 +8015,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>48.791</v>
+        <v>3.946</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -7295,7 +8039,7 @@
         <v>7.2</v>
       </c>
       <c r="N75" t="n">
-        <v>10082</v>
+        <v>10116</v>
       </c>
       <c r="O75" t="n">
         <v>205000000</v>
@@ -7313,20 +8057,30 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
+          <t>['US', 'GB']</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Syncopy']</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>['United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
         <is>
           <t>['English', 'Eesti']</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>https://www.tenetfilm.com/</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Time runs out.</t>
         </is>
@@ -7365,7 +8119,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>82.015</v>
+        <v>4.479</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -7386,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>7.085</v>
+        <v>7.055</v>
       </c>
       <c r="N76" t="n">
-        <v>1454</v>
+        <v>1500</v>
       </c>
       <c r="O76" t="n">
         <v>25000000</v>
@@ -7407,20 +8161,30 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
           <t>['Columbia Pictures', 'Wayfarer Studios', 'Saks Picture Company']</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>https://www.itendswithus.movie</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>We break the pattern or the pattern breaks us.</t>
         </is>
@@ -7459,7 +8223,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>226.648</v>
+        <v>5.181</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7480,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>7.2</v>
+        <v>7.213</v>
       </c>
       <c r="N77" t="n">
-        <v>3368</v>
+        <v>3434</v>
       </c>
       <c r="O77" t="n">
         <v>80000000</v>
@@ -7501,20 +8265,30 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
           <t>['20th Century Studios', 'Scott Free Productions', 'Brandywine Productions']</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>https://www.20thcenturystudios.com/movies/alien-romulus</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>In space, no one can hear you.</t>
         </is>
@@ -7549,7 +8323,7 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>4.728</v>
+        <v>1.505</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7591,16 +8365,26 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
           <t>['Beijing Enlight Pictures']</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="b">
@@ -7635,7 +8419,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>54.722</v>
+        <v>3.845</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7656,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>7</v>
+        <v>7.031</v>
       </c>
       <c r="N79" t="n">
-        <v>2912</v>
+        <v>2932</v>
       </c>
       <c r="O79" t="n">
         <v>100000000</v>
@@ -7677,20 +8461,30 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
           <t>['Lionsgate', 'Color Force', 'about:blank', 'Studio Babelsberg']</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>['Germany', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>https://hungergames.movie/</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>Everyone hungers for something.</t>
         </is>
@@ -7725,7 +8519,7 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>11.419</v>
+        <v>2.965</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7767,16 +8561,26 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
           <t>['Tao Piao Piao', 'As One Production']</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
         <is>
           <t>['English', '普通话']</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="b">
@@ -7784,16 +8588,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>/rOJb0yQOCny0bPjg8bCLw8DyAD7.jpg</t>
+          <t>/mQZJoIhTEkNhCYAqcHrQqhENLdu.jpg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[35, 12, 878]</t>
+          <t>[16, 878, 10751]</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>550988</v>
+        <v>1184918</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -7802,73 +8606,83 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Free Guy</t>
+          <t>The Wild Robot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Un hombre descubre que en realidad es un personaje dentro de un videojuego. Guy (Ryan Reynolds) trabaja como cajero de un banco, es un tipo alegre y solitario al que nada la amarga el día. Incluso si le utilizan como rehén durante un atraco a su banco, él sigue sonriendo como si nada. Pero un día se da cuenta de que Free City no es exactamente la ciudad que él creía. Guy va a descubrir que en realidad es un personaje no jugable dentro de un brutal videojuego. Ahora que sabe que es un personaje de videojuego, Guy, acompañado por Molotov Girl (Jodie Comer), decidirá enfrentarse a todos los villanos que asolan la ciudad.</t>
+          <t>Un robot - ROZZUM unidad 7134, "Roz" para abreviar - naufraga en una isla deshabitada y debe aprender a adaptarse al duro entorno, estableciendo gradualmente relaciones con los animales de la isla y convirtiéndose en la madre adoptiva de un ganso huérfano.</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>70.52200000000001</v>
+        <v>7.35</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>/suaooqn1Mnv60V19MoGxneMupJs.jpg</t>
+          <t>/a0a7RC01aTa7pOnskgJb3mCD2Ba.jpg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Free Guy: Tomando el Control</t>
+          <t>Robot salvaje</t>
         </is>
       </c>
       <c r="L81" t="b">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>7.5</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>8958</v>
+        <v>4538</v>
       </c>
       <c r="O81" t="n">
-        <v>110000000</v>
+        <v>78000000</v>
       </c>
       <c r="P81" t="n">
-        <v>331526598</v>
+        <v>331982078</v>
       </c>
       <c r="Q81" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>['Comedy', 'Adventure', 'Science Fiction']</t>
+          <t>['Animation', 'Science Fiction', 'Family']</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>['Berlanti Productions', '21 Laps Entertainment', 'Maximum Effort', 'Lit Entertainment Group', '20th Century Studios']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
+          <t>['DreamWorks Animation']</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>https://www.20thcenturystudios.com/movies/free-guy</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Life's too short to be a background character.</t>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://www.thewildrobotmovie.com</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Discover your true nature.</t>
         </is>
       </c>
     </row>
@@ -7878,16 +8692,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>/mQZJoIhTEkNhCYAqcHrQqhENLdu.jpg</t>
+          <t>/rOJb0yQOCny0bPjg8bCLw8DyAD7.jpg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[16, 878, 10751]</t>
+          <t>[35, 12, 878]</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1184918</v>
+        <v>550988</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -7896,73 +8710,83 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The Wild Robot</t>
+          <t>Free Guy</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Un robot - ROZZUM unidad 7134, "Roz" para abreviar - naufraga en una isla deshabitada y debe aprender a adaptarse al duro entorno, estableciendo gradualmente relaciones con los animales de la isla y convirtiéndose en la madre adoptiva de un ganso huérfano.</t>
+          <t>Un hombre descubre que en realidad es un personaje dentro de un videojuego. Guy (Ryan Reynolds) trabaja como cajero de un banco, es un tipo alegre y solitario al que nada la amarga el día. Incluso si le utilizan como rehén durante un atraco a su banco, él sigue sonriendo como si nada. Pero un día se da cuenta de que Free City no es exactamente la ciudad que él creía. Guy va a descubrir que en realidad es un personaje no jugable dentro de un brutal videojuego. Ahora que sabe que es un personaje de videojuego, Guy, acompañado por Molotov Girl (Jodie Comer), decidirá enfrentarse a todos los villanos que asolan la ciudad.</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>392.874</v>
+        <v>4.67</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>/a0a7RC01aTa7pOnskgJb3mCD2Ba.jpg</t>
+          <t>/suaooqn1Mnv60V19MoGxneMupJs.jpg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Robot salvaje</t>
+          <t>Free Guy: Tomando el Control</t>
         </is>
       </c>
       <c r="L82" t="b">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>8.300000000000001</v>
+        <v>7.484</v>
       </c>
       <c r="N82" t="n">
-        <v>4411</v>
+        <v>8983</v>
       </c>
       <c r="O82" t="n">
-        <v>78000000</v>
+        <v>110000000</v>
       </c>
       <c r="P82" t="n">
-        <v>324816010</v>
+        <v>331526598</v>
       </c>
       <c r="Q82" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>['Animation', 'Science Fiction', 'Family']</t>
+          <t>['Comedy', 'Adventure', 'Science Fiction']</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>['DreamWorks Animation']</t>
+          <t>['US']</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
+          <t>['Berlanti Productions', '21 Laps Entertainment', 'Maximum Effort', 'Lit Entertainment Group', '20th Century Studios']</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>https://www.thewildrobotmovie.com</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Discover your true nature.</t>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://www.20thcenturystudios.com/movies/free-guy</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Life's too short to be a background character.</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8823,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>37.76</v>
+        <v>4.811</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8020,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>7.9</v>
+        <v>7.938</v>
       </c>
       <c r="N83" t="n">
-        <v>1406</v>
+        <v>1420</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -8041,20 +8865,30 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
+          <t>['JP']</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
           <t>['CoMix Wave Films', 'Story', 'Lawson Entertainment', 'jeki', 'voque ting', 'KADOKAWA', 'Aniplex', 'TOHO']</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>['Japan']</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
         <is>
           <t>['English', '日本語']</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>https://www.suzume-movie.com</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>On the other side of the door, was time in its entirety.</t>
         </is>
@@ -8093,7 +8927,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>125.716</v>
+        <v>4.113</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8114,10 +8948,10 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>7.308</v>
+        <v>7.3</v>
       </c>
       <c r="N84" t="n">
-        <v>9794</v>
+        <v>9826</v>
       </c>
       <c r="O84" t="n">
         <v>85000000</v>
@@ -8135,20 +8969,30 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
           <t>['Original Film', 'Blur Studio', 'Marza Animation Planet', 'Paramount Pictures', 'SEGA', 'SEGA of America']</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>['Japan', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>https://www.paramountmovies.com/movies/sonic-the-hedgehog</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>A whole new speed of hero.</t>
         </is>
@@ -8187,7 +9031,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>129.739</v>
+        <v>3.836</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8208,10 +9052,10 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>7.411</v>
+        <v>7.4</v>
       </c>
       <c r="N85" t="n">
-        <v>1945</v>
+        <v>1954</v>
       </c>
       <c r="O85" t="n">
         <v>72000000</v>
@@ -8229,20 +9073,30 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
           <t>['Universal Pictures', 'Illumination']</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>https://www.migration.movie</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>Odd ducks welcome.</t>
         </is>
@@ -8281,7 +9135,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>48.729</v>
+        <v>4.376</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8302,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>7.5</v>
+        <v>7.474</v>
       </c>
       <c r="N86" t="n">
-        <v>6686</v>
+        <v>6712</v>
       </c>
       <c r="O86" t="n">
         <v>55000000</v>
@@ -8323,20 +9177,30 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
           <t>['Paramount Pictures', 'Platinum Dunes', 'Sunday Night Productions']</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>https://www.aquietplacemovie.com</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Silence is not enough.</t>
         </is>
@@ -8353,7 +9217,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[27, 9648, 53]</t>
+          <t>[27, 53, 9648]</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -8375,7 +9239,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>82.565</v>
+        <v>4.624</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8396,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>7.49</v>
+        <v>7.484</v>
       </c>
       <c r="N87" t="n">
-        <v>4240</v>
+        <v>4259</v>
       </c>
       <c r="O87" t="n">
         <v>20000000</v>
@@ -8412,25 +9276,35 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>['Horror', 'Mystery', 'Thriller']</t>
+          <t>['Horror', 'Thriller', 'Mystery']</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
           <t>['Blumhouse Productions', 'Scott Cawthon Productions']</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="W87" t="inlineStr">
         <is>
           <t>https://www.fivenightsatfreddys.movie</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>Can you survive five nights?</t>
         </is>
@@ -8442,7 +9316,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>/ybn3jCia5XBD0ZgEM07gcUPuRNh.jpg</t>
+          <t>/75nSb1fbWooipwcSU5bUttiOriI.jpg</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -8469,7 +9343,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>72.075</v>
+        <v>4.613</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8490,10 +9364,10 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2036</v>
+        <v>2067</v>
       </c>
       <c r="O88" t="n">
         <v>50000000</v>
@@ -8511,20 +9385,30 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
+          <t>['JP']</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
           <t>['Studio Ghibli']</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>['Japan']</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
         <is>
           <t>['日本語']</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>https://gkids.com/films/the-boy-and-the-heron/</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>Where death comes to an end, life finds a new beginning.</t>
         </is>
@@ -8563,7 +9447,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>34.553</v>
+        <v>3.852</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8584,10 +9468,10 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>7.5</v>
+        <v>7.505</v>
       </c>
       <c r="N89" t="n">
-        <v>3496</v>
+        <v>3512</v>
       </c>
       <c r="O89" t="n">
         <v>85000000</v>
@@ -8605,20 +9489,30 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
+          <t>['AU', 'US']</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Bazmark', 'The Jackal Group']</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>['Australia', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>https://elvis.warnerbros.com</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>The Man. The Legend. The King of Rock &amp; Roll.</t>
         </is>
@@ -8653,7 +9547,7 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>3.24</v>
+        <v>0.34</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8695,16 +9589,26 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
           <t>['Fantawild Animation']</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr">
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
         <is>
           <t>The bears are back in time.</t>
         </is>
@@ -8743,7 +9647,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>45.461</v>
+        <v>3.818</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8764,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>7.116</v>
+        <v>7.1</v>
       </c>
       <c r="N91" t="n">
-        <v>2584</v>
+        <v>2594</v>
       </c>
       <c r="O91" t="n">
         <v>75000000</v>
@@ -8785,20 +9689,30 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
           <t>['Metro-Goldwyn-Mayer', 'Chartoff-Winkler Productions', 'Proximity Media', 'Outlier Society']</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>['English', 'Español']</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>['Español', 'English']</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>https://www.mgmstudios.com/creed-iii</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>You can't run from your past.</t>
         </is>
@@ -8837,7 +9751,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>69.086</v>
+        <v>3.621</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -8858,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.67</v>
+        <v>6.666</v>
       </c>
       <c r="N92" t="n">
-        <v>4418</v>
+        <v>4439</v>
       </c>
       <c r="O92" t="n">
         <v>220000000</v>
@@ -8879,20 +9793,30 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
           <t>['Warner Bros. Pictures', 'Double Dream', 'The Disco Factory', 'DC Films']</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
         <is>
           <t>['English', 'Español', 'Pусский']</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="W92" t="inlineStr">
         <is>
           <t>https://www.dc.com/theflash</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>Worlds collide.</t>
         </is>
@@ -8931,7 +9855,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>66.733</v>
+        <v>4.146</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -8952,10 +9876,10 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6.714</v>
+        <v>6.71</v>
       </c>
       <c r="N93" t="n">
-        <v>2122</v>
+        <v>2131</v>
       </c>
       <c r="O93" t="n">
         <v>38500000</v>
@@ -8973,20 +9897,30 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
           <t>['New Line Cinema', 'Atomic Monster', 'The Safran Company']</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
         <is>
           <t>['Español', 'English', 'Italiano', 'Português', 'Français']</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="W93" t="inlineStr">
         <is>
           <t>https://www.warnerbros.com/movies/nun2</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>Confess your sins.</t>
         </is>
@@ -9025,7 +9959,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>117.917</v>
+        <v>4.239</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -9046,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>6.745</v>
+        <v>6.7</v>
       </c>
       <c r="N94" t="n">
-        <v>2560</v>
+        <v>2596</v>
       </c>
       <c r="O94" t="n">
         <v>67000000</v>
@@ -9067,20 +10001,30 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
           <t>['Paramount Pictures', 'Platinum Dunes', 'Sunday Night Productions']</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="W94" t="inlineStr">
         <is>
           <t>https://www.aquietplacemovie.com</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>Hear how it all began.</t>
         </is>
@@ -9119,7 +10063,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>31.541</v>
+        <v>3.573</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -9161,20 +10105,30 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
           <t>['Taylor Swift Productions', 'Silent House Productions']</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="W95" t="inlineStr">
         <is>
           <t>https://www.tstheerastourfilm.com</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>It's been a long time coming.</t>
         </is>
@@ -9213,7 +10167,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>88.952</v>
+        <v>4.142</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -9234,10 +10188,10 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>7.594</v>
+        <v>7.595</v>
       </c>
       <c r="N96" t="n">
-        <v>9616</v>
+        <v>9639</v>
       </c>
       <c r="O96" t="n">
         <v>135000000</v>
@@ -9255,20 +10209,30 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
           <t>['Walt Disney Animation Studios', 'Walt Disney Pictures']</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
         <is>
           <t>['English', 'Español']</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="W96" t="inlineStr">
         <is>
           <t>https://movies.disney.com/encanto</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>There's a little magic in all of us...almost all of us.</t>
         </is>
@@ -9307,7 +10271,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>20.243</v>
+        <v>3.829</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -9328,10 +10292,10 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>7.787</v>
+        <v>7.749</v>
       </c>
       <c r="N97" t="n">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -9349,20 +10313,30 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
+          <t>['JP']</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
           <t>['Toei Animation', 'Toei Company', 'DandeLion Animation Studio']</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>['Japan']</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
         <is>
           <t>['日本語']</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>http://gkids.com/films/the-first-slam-dunk/</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>17 years and... 40 minutes.</t>
         </is>
@@ -9401,7 +10375,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>82.961</v>
+        <v>3.578</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -9422,10 +10396,10 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>6.3</v>
+        <v>6.321</v>
       </c>
       <c r="N98" t="n">
-        <v>1559</v>
+        <v>1567</v>
       </c>
       <c r="O98" t="n">
         <v>175000000</v>
@@ -9443,20 +10417,30 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
+          <t>['US']</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
           <t>['Walt Disney Pictures', 'Walt Disney Animation Studios']</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>['United States of America']</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="W98" t="inlineStr">
         <is>
           <t>https://movies.disney.com/wish</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>Be careful what you wish for.</t>
         </is>
@@ -9495,7 +10479,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>153.942</v>
+        <v>3.606</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -9516,10 +10500,10 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>7.086</v>
+        <v>7.078</v>
       </c>
       <c r="N99" t="n">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="O99" t="n">
         <v>60000000</v>
@@ -9537,20 +10521,30 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
+          <t>['US', 'GB']</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
           <t>['Alcon Entertainment', 'DNEG', 'Wayfarer Studios', 'One Cool Group', 'Stage 6 Films', 'Andrews McMeel Entertainment', 'John Cohen Productions']</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>['Hong Kong', 'United Kingdom', 'United States of America']</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
         <is>
           <t>['English']</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>https://www.thegarfield-movie.com/</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>Indoor cat. Outdoor adventure.</t>
         </is>
@@ -9589,7 +10583,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5.936</v>
+        <v>1.364</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -9613,7 +10607,7 @@
         <v>7.4</v>
       </c>
       <c r="N100" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O100" t="n">
         <v>8800000</v>
@@ -9631,16 +10625,26 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
           <t>['Lian Ray Pictures', 'Zhejiang Hengdian Film Production', 'China Film Group Corporation', 'Tianjin Maoyan Weiying Culture Media', 'Tao Piao Piao', 'Weibo Corporation']</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="b">
@@ -9648,7 +10652,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>/zXyYAcZmTh1l6jaJzl8cxP5NN9P.jpg</t>
+          <t>/q4y0PmDGRX193kfdtVk26O7Ujrk.jpg</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9671,7 +10675,7 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>8.25</v>
+        <v>1.695</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -9692,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>7.5</v>
+        <v>7.542</v>
       </c>
       <c r="N101" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -9704,7 +10708,7 @@
         <v>252520750</v>
       </c>
       <c r="Q101" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -9713,16 +10717,26 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
+          <t>['CN']</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
           <t>['Light Chaser Animation Studios']</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>['China']</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
         <is>
           <t>['普通话']</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -7024,10 +7024,10 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6.8</v>
+        <v>6.828</v>
       </c>
       <c r="N65" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="O65" t="n">
         <v>200000000</v>
@@ -7943,7 +7943,7 @@
         <v>7.085</v>
       </c>
       <c r="N74" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O74" t="n">
         <v>85000000</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.167</v>
+        <v>26.3784</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>7.606</v>
+        <v>7.607</v>
       </c>
       <c r="N2" t="n">
-        <v>12339</v>
+        <v>12403</v>
       </c>
       <c r="O2" t="n">
         <v>460000000</v>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.295</v>
+        <v>29.0789</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.948</v>
+        <v>7.947</v>
       </c>
       <c r="N3" t="n">
-        <v>20589</v>
+        <v>20634</v>
       </c>
       <c r="O3" t="n">
         <v>200000000</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.305</v>
+        <v>53.9804</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.6</v>
+        <v>7.557</v>
       </c>
       <c r="N4" t="n">
-        <v>5647</v>
+        <v>5698</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.948</v>
+        <v>30.1254</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.183999999999999</v>
+        <v>8.182</v>
       </c>
       <c r="N5" t="n">
-        <v>9646</v>
+        <v>9685</v>
       </c>
       <c r="O5" t="n">
         <v>170000000</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5.677</v>
+        <v>22.6255</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.982</v>
+        <v>6.981</v>
       </c>
       <c r="N6" t="n">
-        <v>9666</v>
+        <v>9730</v>
       </c>
       <c r="O6" t="n">
         <v>145000000</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[16, 10751, 12, 14, 35]</t>
+          <t>[10751, 35, 12, 16]</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.845</v>
+        <v>26.1428</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.627</v>
+        <v>7.626</v>
       </c>
       <c r="N7" t="n">
-        <v>9517</v>
+        <v>9554</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['Animación', 'Familia', 'Aventura', 'Fantasía', 'Comedia']</t>
+          <t>['Familia', 'Comedia', 'Aventura', 'Animación']</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.328</v>
+        <v>66.9084</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>/347cCxyMXy8WkcHfsfaPaugCyPA.jpg</t>
+          <t>/9TFSqghEHrlBMRR63yTx80Orxva.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.614</v>
+        <v>7.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6881</v>
+        <v>6968</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11.844</v>
+        <v>220.0556</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.153</v>
+        <v>7.118</v>
       </c>
       <c r="N9" t="n">
-        <v>1917</v>
+        <v>2096</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.097</v>
+        <v>18.5198</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.674</v>
+        <v>6.7</v>
       </c>
       <c r="N10" t="n">
-        <v>6273</v>
+        <v>6297</v>
       </c>
       <c r="O10" t="n">
         <v>165000000</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.572</v>
+        <v>63.4427</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.1</v>
+        <v>7.054</v>
       </c>
       <c r="N11" t="n">
-        <v>2626</v>
+        <v>2659</v>
       </c>
       <c r="O11" t="n">
         <v>100000000</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.851</v>
+        <v>17.0531</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.265</v>
+        <v>7.262</v>
       </c>
       <c r="N12" t="n">
-        <v>9399</v>
+        <v>9436</v>
       </c>
       <c r="O12" t="n">
         <v>200000000</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.05</v>
+        <v>28.9731</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1</v>
+        <v>8.066000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9941</v>
+        <v>10025</v>
       </c>
       <c r="O13" t="n">
         <v>100000000</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.802</v>
+        <v>11.7687</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.3</v>
+        <v>7.301</v>
       </c>
       <c r="N14" t="n">
-        <v>3687</v>
+        <v>3696</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3.546</v>
+        <v>1.0514</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>5.917</v>
       </c>
       <c r="N15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O15" t="n">
         <v>200000000</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.888</v>
+        <v>18.8961</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.07</v>
+        <v>7.068</v>
       </c>
       <c r="N16" t="n">
-        <v>6707</v>
+        <v>6743</v>
       </c>
       <c r="O16" t="n">
         <v>250000000</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.875</v>
+        <v>17.6654</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7.949</v>
+        <v>7.9</v>
       </c>
       <c r="N17" t="n">
-        <v>7189</v>
+        <v>7227</v>
       </c>
       <c r="O17" t="n">
         <v>250000000</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>3.544</v>
+        <v>0.6823</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>7.031</v>
       </c>
       <c r="N18" t="n">
         <v>147</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4.135</v>
+        <v>9.388299999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>7.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6427</v>
+        <v>6456</v>
       </c>
       <c r="O19" t="n">
         <v>250000000</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>['English', 'Français', 'Italiano', 'Pусский', 'Español']</t>
+          <t>['Pусский', 'Français', 'Español', 'Italiano', 'English']</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.013</v>
+        <v>18.8743</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>7.7</v>
       </c>
       <c r="N20" t="n">
-        <v>10721</v>
+        <v>10771</v>
       </c>
       <c r="O20" t="n">
         <v>185000000</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.095</v>
+        <v>13.4407</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.421</v>
+        <v>6.42</v>
       </c>
       <c r="N21" t="n">
-        <v>7789</v>
+        <v>7825</v>
       </c>
       <c r="O21" t="n">
         <v>250000000</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4.492</v>
+        <v>39.9075</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.907</v>
+        <v>6.928</v>
       </c>
       <c r="N22" t="n">
-        <v>1927</v>
+        <v>1990</v>
       </c>
       <c r="O22" t="n">
         <v>150000000</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.783</v>
+        <v>8.897500000000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>7.1</v>
       </c>
       <c r="N23" t="n">
-        <v>7298</v>
+        <v>7315</v>
       </c>
       <c r="O23" t="n">
         <v>200000000</v>
@@ -2796,16 +2796,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/xOMo8BRK7PfcJv9JCnx7s5hj0PX.jpg</t>
+          <t>/1w8kutrRucTd3wlYyu5QlUDMiG1.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[878, 12]</t>
+          <t>[12, 10751, 16]</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>693134</v>
+        <v>762509</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2814,53 +2814,53 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dune: Part Two</t>
+          <t>Mufasa: The Lion King</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sigue la mítica jornada de Paul Atreides mientras se une con Chani y los Fremen en su camino hacia la venganza contra los conspiradores que destruyeron a su familia. Enfrentado a una elección entre el amor de su vida y el destino del universo conocido, Paul se esfuerza por prevenir un terrible futuro que solo él puede prever.</t>
+          <t>Mufasa era un cachorro huérfano, perdido y solo hasta que conoce a un simpático león llamado Taka, heredero de un linaje real. Este encuentro casual pone en marcha un viaje de un extraordinario grupo de inadaptados que buscan su destino.</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.664</v>
+        <v>238.3487</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>/xCHmhHeO7aOCMlzcNukGH6Q7EiD.jpg</t>
+          <t>/dmw74cWIEKaEgl5Dv3kUTcCob6D.jpg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Duna: Parte dos</t>
+          <t>Mufasa: El rey león</t>
         </is>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>8.1</v>
+        <v>7.449</v>
       </c>
       <c r="N24" t="n">
-        <v>6418</v>
+        <v>1799</v>
       </c>
       <c r="O24" t="n">
-        <v>190000000</v>
+        <v>200000000</v>
       </c>
       <c r="P24" t="n">
-        <v>714444358</v>
+        <v>717197856</v>
       </c>
       <c r="Q24" t="n">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['Science Fiction', 'Adventure']</t>
+          <t>['Adventure', 'Family', 'Animation']</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>['Legendary Pictures']</t>
+          <t>['Walt Disney Pictures']</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>https://www.dunemovie.com</t>
+          <t>https://movies.disney.com/mufasa-the-lion-king</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Long live the fighters.</t>
+          <t>The story of an orphan who would be king.</t>
         </is>
       </c>
     </row>
@@ -2900,16 +2900,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/4XM8DUTQb3lhLemJC51Jx4a2EuA.jpg</t>
+          <t>/xOMo8BRK7PfcJv9JCnx7s5hj0PX.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[28, 80, 53, 12, 9648]</t>
+          <t>[878, 12]</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>385687</v>
+        <v>693134</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2918,53 +2918,53 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fast X</t>
+          <t>Dune: Part Two</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A través de varias misiones y contra lo imposible, Dom Toretto y su familia han sido más astutos y más rápidos que todos los enemigos se le han cruzado en su camino. Ahora se enfrentan a su enemigo más letal: una amenaza aterradora que surge de las sombras del pasado que está alimentado de una venganza sangrienta, y está decidido a destruir a su familia y destruir todo, y a cualquier persona, a los que Dom ama.</t>
+          <t>Sigue la mítica jornada de Paul Atreides mientras se une con Chani y los Fremen en su camino hacia la venganza contra los conspiradores que destruyeron a su familia. Enfrentado a una elección entre el amor de su vida y el destino del universo conocido, Paul se esfuerza por prevenir un terrible futuro que solo él puede prever.</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.962</v>
+        <v>25.6541</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>/3P9QvWVN02Etn4kYGC702WVoXEb.jpg</t>
+          <t>/xCHmhHeO7aOCMlzcNukGH6Q7EiD.jpg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Rápidos y furiosos X</t>
+          <t>Duna: Parte dos</t>
         </is>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>7.05</v>
+        <v>8.1</v>
       </c>
       <c r="N25" t="n">
-        <v>5814</v>
+        <v>6476</v>
       </c>
       <c r="O25" t="n">
-        <v>340000000</v>
+        <v>190000000</v>
       </c>
       <c r="P25" t="n">
-        <v>704709660</v>
+        <v>714444358</v>
       </c>
       <c r="Q25" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['Action', 'Crime', 'Thriller', 'Adventure', 'Mystery']</t>
+          <t>['Science Fiction', 'Adventure']</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>['Universal Pictures', 'Original Film', 'One Race', 'Perfect Storm Entertainment']</t>
+          <t>['Legendary Pictures']</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2984,17 +2984,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>['English', 'Español']</t>
+          <t>['English']</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>https://fastxmovie.com</t>
+          <t>https://www.dunemovie.com</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>The end of the road begins.</t>
+          <t>Long live the fighters.</t>
         </is>
       </c>
     </row>
@@ -3004,16 +3004,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/1w8kutrRucTd3wlYyu5QlUDMiG1.jpg</t>
+          <t>/4XM8DUTQb3lhLemJC51Jx4a2EuA.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[12, 10751, 16]</t>
+          <t>[28, 80, 53, 12, 9648]</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>762509</v>
+        <v>385687</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3022,53 +3022,53 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mufasa: The Lion King</t>
+          <t>Fast X</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mufasa era un cachorro huérfano, perdido y solo hasta que conoce a un simpático león llamado Taka, heredero de un linaje real. Este encuentro casual pone en marcha un viaje de un extraordinario grupo de inadaptados que buscan su destino.</t>
+          <t>A través de varias misiones y contra lo imposible, Dom Toretto y su familia han sido más astutos y más rápidos que todos los enemigos se le han cruzado en su camino. Ahora se enfrentan a su enemigo más letal: una amenaza aterradora que surge de las sombras del pasado que está alimentado de una venganza sangrienta, y está decidido a destruir a su familia y destruir todo, y a cualquier persona, a los que Dom ama.</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10.95</v>
+        <v>36.1685</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>/dmw74cWIEKaEgl5Dv3kUTcCob6D.jpg</t>
+          <t>/3P9QvWVN02Etn4kYGC702WVoXEb.jpg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mufasa: El rey león</t>
+          <t>Rápidos y furiosos X</t>
         </is>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7.469</v>
+        <v>7.049</v>
       </c>
       <c r="N26" t="n">
-        <v>1652</v>
+        <v>5828</v>
       </c>
       <c r="O26" t="n">
-        <v>200000000</v>
+        <v>340000000</v>
       </c>
       <c r="P26" t="n">
-        <v>700197856</v>
+        <v>704709660</v>
       </c>
       <c r="Q26" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['Adventure', 'Family', 'Animation']</t>
+          <t>['Action', 'Crime', 'Thriller', 'Adventure', 'Mystery']</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>['Walt Disney Pictures']</t>
+          <t>['Universal Pictures', 'Original Film', 'One Race', 'Perfect Storm Entertainment']</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>['English']</t>
+          <t>['Español', 'English']</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>https://movies.disney.com/mufasa-the-lion-king</t>
+          <t>https://fastxmovie.com</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>The story of an orphan who would be king.</t>
+          <t>The end of the road begins.</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.741</v>
+        <v>27.0356</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.343</v>
       </c>
       <c r="N27" t="n">
-        <v>7383</v>
+        <v>7424</v>
       </c>
       <c r="O27" t="n">
         <v>100000000</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/ihBzrXY1R8MDnT1JMWatrMjqUY6.jpg</t>
+          <t>/j3P4MhXTIrb9wPX1hqQQtpegxXP.jpg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>3.014</v>
+        <v>1.5593</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>5.6</v>
       </c>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O28" t="n">
         <v>117000000</v>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.558</v>
+        <v>0.8041</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3352,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.9</v>
+        <v>5.927</v>
       </c>
       <c r="N29" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.704</v>
+        <v>15.6611</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7.1</v>
+        <v>7.084</v>
       </c>
       <c r="N30" t="n">
-        <v>3795</v>
+        <v>3817</v>
       </c>
       <c r="O30" t="n">
         <v>125000000</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.596</v>
+        <v>1.4814</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6.2</v>
+        <v>6.209</v>
       </c>
       <c r="N31" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
         <v>200000000</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.845</v>
+        <v>7.075</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>7.278</v>
+        <v>7.279</v>
       </c>
       <c r="N32" t="n">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="O32" t="n">
         <v>73800000</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.962</v>
+        <v>27.3889</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>7.1</v>
+        <v>7.099</v>
       </c>
       <c r="N33" t="n">
-        <v>4094</v>
+        <v>4119</v>
       </c>
       <c r="O33" t="n">
         <v>150000000</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.609</v>
+        <v>16.1477</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6.317</v>
+        <v>6.313</v>
       </c>
       <c r="N34" t="n">
-        <v>3015</v>
+        <v>3027</v>
       </c>
       <c r="O34" t="n">
         <v>297000000</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.944</v>
+        <v>20.5353</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7.531</v>
+        <v>7.532</v>
       </c>
       <c r="N35" t="n">
-        <v>4080</v>
+        <v>4106</v>
       </c>
       <c r="O35" t="n">
         <v>291000000</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.891</v>
+        <v>28.6923</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>7.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2998</v>
+        <v>3015</v>
       </c>
       <c r="O36" t="n">
         <v>80000000</v>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.422</v>
+        <v>10.3945</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="N37" t="n">
-        <v>4034</v>
+        <v>4043</v>
       </c>
       <c r="O37" t="n">
         <v>15700000</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.67</v>
+        <v>11.6245</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6.777</v>
+        <v>6.8</v>
       </c>
       <c r="N38" t="n">
-        <v>10548</v>
+        <v>10571</v>
       </c>
       <c r="O38" t="n">
         <v>110000000</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>['Español', 'English']</t>
+          <t>['English', 'Español']</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.804</v>
+        <v>1.5695</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6.199</v>
+        <v>6.2</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4.381</v>
+        <v>19.5832</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>7.618</v>
       </c>
       <c r="N40" t="n">
-        <v>4711</v>
+        <v>4734</v>
       </c>
       <c r="O40" t="n">
         <v>200000000</v>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.217</v>
+        <v>150.0364</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.721</v>
+        <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2188</v>
+        <v>2297</v>
       </c>
       <c r="O41" t="n">
         <v>122000000</v>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4.471</v>
+        <v>21.7922</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4680,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>8052</v>
+        <v>8074</v>
       </c>
       <c r="O42" t="n">
         <v>90000000</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.705</v>
+        <v>1.6015</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="N43" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O43" t="n">
         <v>100000000</v>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5.662</v>
+        <v>84.6773</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.796</v>
+        <v>6.8</v>
       </c>
       <c r="N44" t="n">
-        <v>3029</v>
+        <v>3108</v>
       </c>
       <c r="O44" t="n">
         <v>120000000</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4.157</v>
+        <v>10.9634</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>6.3</v>
+        <v>6.295</v>
       </c>
       <c r="N45" t="n">
-        <v>5178</v>
+        <v>5201</v>
       </c>
       <c r="O45" t="n">
         <v>388369742</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>2.036</v>
+        <v>1.4358</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>6.964</v>
       </c>
       <c r="N46" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.082</v>
+        <v>8.297599999999999</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.582</v>
+        <v>7.579</v>
       </c>
       <c r="N47" t="n">
-        <v>10113</v>
+        <v>10142</v>
       </c>
       <c r="O47" t="n">
         <v>200000000</v>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>2.07</v>
+        <v>1.2248</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>7.246</v>
+        <v>7.1</v>
       </c>
       <c r="N48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.792</v>
+        <v>1.8966</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>6.9</v>
       </c>
       <c r="N49" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O49" t="n">
         <v>80000000</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>3.023</v>
+        <v>0.6466</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>6.9</v>
       </c>
       <c r="N50" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6.648</v>
+        <v>71.5954</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>6.774</v>
+        <v>6.765</v>
       </c>
       <c r="N51" t="n">
-        <v>3033</v>
+        <v>3103</v>
       </c>
       <c r="O51" t="n">
         <v>310000000</v>
@@ -5588,7 +5588,7 @@
         <v>458718000</v>
       </c>
       <c r="Q51" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[35, 14, 27]</t>
+          <t>[27, 35, 14]</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.748</v>
+        <v>15.2978</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5680,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7.045</v>
+        <v>7.042</v>
       </c>
       <c r="N52" t="n">
-        <v>2379</v>
+        <v>2405</v>
       </c>
       <c r="O52" t="n">
         <v>100000000</v>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>['Comedy', 'Fantasy', 'Horror']</t>
+          <t>['Horror', 'Comedy', 'Fantasy']</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3.819</v>
+        <v>20.2842</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.248</v>
+        <v>7.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4834</v>
+        <v>4846</v>
       </c>
       <c r="O53" t="n">
         <v>195000000</v>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>4.445</v>
+        <v>27.0149</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>7.7</v>
       </c>
       <c r="N54" t="n">
-        <v>6896</v>
+        <v>6932</v>
       </c>
       <c r="O54" t="n">
         <v>90000000</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.679</v>
+        <v>14.852</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>6.6</v>
+        <v>6.611</v>
       </c>
       <c r="N55" t="n">
-        <v>2992</v>
+        <v>3004</v>
       </c>
       <c r="O55" t="n">
         <v>205000000</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.156</v>
+        <v>15.9028</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>7.526</v>
+        <v>7.523</v>
       </c>
       <c r="N56" t="n">
-        <v>9600</v>
+        <v>9642</v>
       </c>
       <c r="O56" t="n">
         <v>150000000</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.047</v>
+        <v>0.1385</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>4.622</v>
+        <v>12.3445</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6296,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.135</v>
+        <v>7.134</v>
       </c>
       <c r="N58" t="n">
-        <v>8363</v>
+        <v>8373</v>
       </c>
       <c r="O58" t="n">
         <v>90000000</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>4.086</v>
+        <v>11.9223</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6400,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="N59" t="n">
-        <v>4469</v>
+        <v>4476</v>
       </c>
       <c r="O59" t="n">
         <v>85000000</v>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6.354</v>
+        <v>24.7169</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>7.782</v>
       </c>
       <c r="N60" t="n">
-        <v>13304</v>
+        <v>13362</v>
       </c>
       <c r="O60" t="n">
         <v>165000000</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.867</v>
+        <v>14.9264</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>6.647</v>
+        <v>6.6</v>
       </c>
       <c r="N61" t="n">
-        <v>4627</v>
+        <v>4650</v>
       </c>
       <c r="O61" t="n">
         <v>200000000</v>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.402</v>
+        <v>10.6744</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6712,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6.916</v>
+        <v>6.913</v>
       </c>
       <c r="N62" t="n">
-        <v>6165</v>
+        <v>6194</v>
       </c>
       <c r="O62" t="n">
         <v>120000000</v>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.855</v>
+        <v>24.2806</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>7.474</v>
+        <v>7.472</v>
       </c>
       <c r="N63" t="n">
-        <v>5394</v>
+        <v>5420</v>
       </c>
       <c r="O63" t="n">
         <v>110000000</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4.226</v>
+        <v>36.3891</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>7.383</v>
+        <v>7.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2795</v>
+        <v>2814</v>
       </c>
       <c r="O64" t="n">
         <v>100000000</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>/oaLl6puFpgisUF3bXT5h0g29d07.jpg</t>
+          <t>/c6H7Z4u73ir3cIoCteuhJh7UCAR.jpg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4.858</v>
+        <v>10.0214</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7024,10 +7024,10 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6.828</v>
+        <v>6.8</v>
       </c>
       <c r="N65" t="n">
-        <v>8454</v>
+        <v>8481</v>
       </c>
       <c r="O65" t="n">
         <v>200000000</v>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>0.028</v>
+        <v>0.0071</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3.919</v>
+        <v>23.8669</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7220,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>7.083</v>
+        <v>7.1</v>
       </c>
       <c r="N67" t="n">
-        <v>3617</v>
+        <v>3644</v>
       </c>
       <c r="O67" t="n">
         <v>160000000</v>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>4.074</v>
+        <v>11.9891</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>6.9</v>
       </c>
       <c r="N68" t="n">
-        <v>6461</v>
+        <v>6479</v>
       </c>
       <c r="O68" t="n">
         <v>200000000</v>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1.431</v>
+        <v>0.8423</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>6.2</v>
       </c>
       <c r="N69" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.606</v>
+        <v>16.1703</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>6.449</v>
+        <v>6.4</v>
       </c>
       <c r="N70" t="n">
-        <v>3534</v>
+        <v>3544</v>
       </c>
       <c r="O70" t="n">
         <v>129000000</v>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>4.655</v>
+        <v>10.8733</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6.6</v>
+        <v>6.559</v>
       </c>
       <c r="N71" t="n">
-        <v>3579</v>
+        <v>3600</v>
       </c>
       <c r="O71" t="n">
         <v>294700000</v>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4.137</v>
+        <v>15.8599</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7.212</v>
+        <v>7.2</v>
       </c>
       <c r="N72" t="n">
-        <v>10384</v>
+        <v>10415</v>
       </c>
       <c r="O72" t="n">
         <v>200000000</v>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>4.35</v>
+        <v>19.391</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>6.857</v>
+        <v>6.856</v>
       </c>
       <c r="N73" t="n">
-        <v>2293</v>
+        <v>2336</v>
       </c>
       <c r="O73" t="n">
         <v>155000000</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3.817</v>
+        <v>6.6178</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -7940,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>7.085</v>
+        <v>7.1</v>
       </c>
       <c r="N74" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O74" t="n">
         <v>85000000</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3.946</v>
+        <v>10.1228</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -8036,10 +8036,10 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>7.2</v>
+        <v>7.182</v>
       </c>
       <c r="N75" t="n">
-        <v>10116</v>
+        <v>10149</v>
       </c>
       <c r="O75" t="n">
         <v>205000000</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4.479</v>
+        <v>15.6867</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -8140,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>7.055</v>
+        <v>7.047</v>
       </c>
       <c r="N76" t="n">
-        <v>1500</v>
+        <v>1535</v>
       </c>
       <c r="O76" t="n">
         <v>25000000</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5.181</v>
+        <v>35.4648</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>7.213</v>
+        <v>7.214</v>
       </c>
       <c r="N77" t="n">
-        <v>3434</v>
+        <v>3484</v>
       </c>
       <c r="O77" t="n">
         <v>80000000</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>1.505</v>
+        <v>0.9338</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -8344,10 +8344,10 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="N78" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>3.845</v>
+        <v>16.8721</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>7.031</v>
+        <v>7.027</v>
       </c>
       <c r="N79" t="n">
-        <v>2932</v>
+        <v>2960</v>
       </c>
       <c r="O79" t="n">
         <v>100000000</v>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>2.965</v>
+        <v>1.1791</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>6.5</v>
       </c>
       <c r="N80" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O80" t="n">
         <v>9500000</v>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>7.35</v>
+        <v>58.4281</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>8.337999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>4538</v>
+        <v>4616</v>
       </c>
       <c r="O81" t="n">
         <v>78000000</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>4.67</v>
+        <v>8.3955</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -8740,10 +8740,10 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>7.484</v>
+        <v>7.483</v>
       </c>
       <c r="N82" t="n">
-        <v>8983</v>
+        <v>9007</v>
       </c>
       <c r="O82" t="n">
         <v>110000000</v>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>4.811</v>
+        <v>6.544</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>7.938</v>
+        <v>7.931</v>
       </c>
       <c r="N83" t="n">
-        <v>1420</v>
+        <v>1436</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>4.113</v>
+        <v>16.5439</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>7.3</v>
       </c>
       <c r="N84" t="n">
-        <v>9826</v>
+        <v>9850</v>
       </c>
       <c r="O84" t="n">
         <v>85000000</v>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>3.836</v>
+        <v>22.9018</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>7.4</v>
       </c>
       <c r="N85" t="n">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="O85" t="n">
         <v>72000000</v>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.376</v>
+        <v>10.6737</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>7.474</v>
+        <v>7.5</v>
       </c>
       <c r="N86" t="n">
-        <v>6712</v>
+        <v>6733</v>
       </c>
       <c r="O86" t="n">
         <v>55000000</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[27, 53, 9648]</t>
+          <t>[27, 53]</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>4.624</v>
+        <v>13.6723</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>7.484</v>
       </c>
       <c r="N87" t="n">
-        <v>4259</v>
+        <v>4270</v>
       </c>
       <c r="O87" t="n">
         <v>20000000</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>['Horror', 'Thriller', 'Mystery']</t>
+          <t>['Horror', 'Thriller']</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>4.613</v>
+        <v>19.0707</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="N88" t="n">
-        <v>2067</v>
+        <v>2104</v>
       </c>
       <c r="O88" t="n">
         <v>50000000</v>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>3.852</v>
+        <v>5.6411</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -9468,10 +9468,10 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>7.505</v>
+        <v>7.5</v>
       </c>
       <c r="N89" t="n">
-        <v>3512</v>
+        <v>3530</v>
       </c>
       <c r="O89" t="n">
         <v>85000000</v>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0.34</v>
+        <v>0.8388</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>3.818</v>
+        <v>8.0509</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>7.1</v>
       </c>
       <c r="N91" t="n">
-        <v>2594</v>
+        <v>2603</v>
       </c>
       <c r="O91" t="n">
         <v>75000000</v>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3.621</v>
+        <v>16.0048</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.666</v>
+        <v>6.662</v>
       </c>
       <c r="N92" t="n">
-        <v>4439</v>
+        <v>4466</v>
       </c>
       <c r="O92" t="n">
         <v>220000000</v>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>4.146</v>
+        <v>15.4765</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6.71</v>
+        <v>6.711</v>
       </c>
       <c r="N93" t="n">
-        <v>2131</v>
+        <v>2139</v>
       </c>
       <c r="O93" t="n">
         <v>38500000</v>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>4.239</v>
+        <v>24.7039</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>6.7</v>
+        <v>6.741</v>
       </c>
       <c r="N94" t="n">
-        <v>2596</v>
+        <v>2656</v>
       </c>
       <c r="O94" t="n">
         <v>67000000</v>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3.573</v>
+        <v>3.4188</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>8.199999999999999</v>
+        <v>8.259</v>
       </c>
       <c r="N95" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="O95" t="n">
         <v>15000000</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>4.142</v>
+        <v>17.6489</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>7.595</v>
       </c>
       <c r="N96" t="n">
-        <v>9639</v>
+        <v>9658</v>
       </c>
       <c r="O96" t="n">
         <v>135000000</v>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>3.829</v>
+        <v>3.9327</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>7.749</v>
       </c>
       <c r="N97" t="n">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3.578</v>
+        <v>12.7589</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -10396,10 +10396,10 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>6.321</v>
+        <v>6.3</v>
       </c>
       <c r="N98" t="n">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="O98" t="n">
         <v>175000000</v>
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.606</v>
+        <v>23.5052</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -10500,10 +10500,10 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>7.078</v>
+        <v>7.1</v>
       </c>
       <c r="N99" t="n">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="O99" t="n">
         <v>60000000</v>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.364</v>
+        <v>0.2619</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>1.695</v>
+        <v>1.3008</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>7.542</v>
+        <v>7.6</v>
       </c>
       <c r="N101" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>26.3784</v>
+        <v>25.4995</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>7.607</v>
+        <v>7.608</v>
       </c>
       <c r="N2" t="n">
-        <v>12403</v>
+        <v>12427</v>
       </c>
       <c r="O2" t="n">
         <v>460000000</v>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>29.0789</v>
+        <v>29.1545</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.947</v>
+        <v>7.946</v>
       </c>
       <c r="N3" t="n">
-        <v>20634</v>
+        <v>20654</v>
       </c>
       <c r="O3" t="n">
         <v>200000000</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>53.9804</v>
+        <v>52.8141</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.557</v>
+        <v>7.556</v>
       </c>
       <c r="N4" t="n">
-        <v>5698</v>
+        <v>5713</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30.1254</v>
+        <v>34.2236</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.182</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9685</v>
+        <v>9705</v>
       </c>
       <c r="O5" t="n">
         <v>170000000</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22.6255</v>
+        <v>22.8885</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.981</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>9730</v>
+        <v>9750</v>
       </c>
       <c r="O6" t="n">
         <v>145000000</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26.1428</v>
+        <v>26.3238</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.626</v>
+        <v>7.6</v>
       </c>
       <c r="N7" t="n">
-        <v>9554</v>
+        <v>9568</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>66.9084</v>
+        <v>61.4447</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.6</v>
+        <v>7.608</v>
       </c>
       <c r="N8" t="n">
-        <v>6968</v>
+        <v>7000</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>220.0556</v>
+        <v>182.5604</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.118</v>
+        <v>7.108</v>
       </c>
       <c r="N9" t="n">
-        <v>2096</v>
+        <v>2139</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
       </c>
       <c r="P9" t="n">
-        <v>1056396565</v>
+        <v>1059544057</v>
       </c>
       <c r="Q9" t="n">
         <v>99</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18.5198</v>
+        <v>17.5589</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>6.7</v>
       </c>
       <c r="N10" t="n">
-        <v>6297</v>
+        <v>6303</v>
       </c>
       <c r="O10" t="n">
         <v>165000000</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>63.4427</v>
+        <v>62.0002</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.054</v>
+        <v>7.051</v>
       </c>
       <c r="N11" t="n">
-        <v>2659</v>
+        <v>2668</v>
       </c>
       <c r="O11" t="n">
         <v>100000000</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17.0531</v>
+        <v>17.6728</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.262</v>
+        <v>7.264</v>
       </c>
       <c r="N12" t="n">
-        <v>9436</v>
+        <v>9452</v>
       </c>
       <c r="O12" t="n">
         <v>200000000</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/nb3xI8XI3w4pMVZ38VijbsyBqP4.jpg</t>
+          <t>/neeNHeXjMF5fXoCJRsOmkNGC7q.jpg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>28.9731</v>
+        <v>30.6966</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.066000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="N13" t="n">
-        <v>10025</v>
+        <v>10057</v>
       </c>
       <c r="O13" t="n">
         <v>100000000</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11.7687</v>
+        <v>11.6528</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.301</v>
+        <v>7.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3696</v>
+        <v>3699</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1.0514</v>
+        <v>1.242</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18.8961</v>
+        <v>17.1932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.068</v>
+        <v>7.067</v>
       </c>
       <c r="N16" t="n">
-        <v>6743</v>
+        <v>6756</v>
       </c>
       <c r="O16" t="n">
         <v>250000000</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17.6654</v>
+        <v>17.562</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7.9</v>
+        <v>7.948</v>
       </c>
       <c r="N17" t="n">
-        <v>7227</v>
+        <v>7242</v>
       </c>
       <c r="O17" t="n">
         <v>250000000</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.6823</v>
+        <v>0.7501</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.388299999999999</v>
+        <v>10.1007</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7.4</v>
+        <v>7.365</v>
       </c>
       <c r="N19" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="O19" t="n">
         <v>250000000</v>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>18.8743</v>
+        <v>20.5049</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.7</v>
+        <v>7.655</v>
       </c>
       <c r="N20" t="n">
-        <v>10771</v>
+        <v>10785</v>
       </c>
       <c r="O20" t="n">
         <v>185000000</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>13.4407</v>
+        <v>14.6281</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>6.42</v>
       </c>
       <c r="N21" t="n">
-        <v>7825</v>
+        <v>7836</v>
       </c>
       <c r="O21" t="n">
         <v>250000000</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.9075</v>
+        <v>39.5869</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2636,16 +2636,16 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.928</v>
+        <v>6.933</v>
       </c>
       <c r="N22" t="n">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="O22" t="n">
         <v>150000000</v>
       </c>
       <c r="P22" t="n">
-        <v>728145850</v>
+        <v>747289164</v>
       </c>
       <c r="Q22" t="n">
         <v>162</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>8.897500000000001</v>
+        <v>8.6699</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>7.1</v>
+        <v>7.054</v>
       </c>
       <c r="N23" t="n">
-        <v>7315</v>
+        <v>7325</v>
       </c>
       <c r="O23" t="n">
         <v>200000000</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>238.3487</v>
+        <v>181.448</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2844,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.449</v>
+        <v>7.444</v>
       </c>
       <c r="N24" t="n">
-        <v>1799</v>
+        <v>1862</v>
       </c>
       <c r="O24" t="n">
         <v>200000000</v>
       </c>
       <c r="P24" t="n">
-        <v>717197856</v>
+        <v>721046090</v>
       </c>
       <c r="Q24" t="n">
         <v>118</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>25.6541</v>
+        <v>28.2372</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>8.1</v>
       </c>
       <c r="N25" t="n">
-        <v>6476</v>
+        <v>6494</v>
       </c>
       <c r="O25" t="n">
         <v>190000000</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>36.1685</v>
+        <v>35.6408</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>7.049</v>
       </c>
       <c r="N26" t="n">
-        <v>5828</v>
+        <v>5834</v>
       </c>
       <c r="O26" t="n">
         <v>340000000</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>27.0356</v>
+        <v>29.7516</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>8.343</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>7424</v>
+        <v>7450</v>
       </c>
       <c r="O27" t="n">
         <v>100000000</v>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1.5593</v>
+        <v>1.4777</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.8041</v>
+        <v>0.8331</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15.6611</v>
+        <v>16.6254</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3448,16 +3448,16 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7.084</v>
+        <v>7.086</v>
       </c>
       <c r="N30" t="n">
-        <v>3817</v>
+        <v>3823</v>
       </c>
       <c r="O30" t="n">
         <v>125000000</v>
       </c>
       <c r="P30" t="n">
-        <v>632302312</v>
+        <v>634502312</v>
       </c>
       <c r="Q30" t="n">
         <v>117</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.4814</v>
+        <v>1.6006</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7.075</v>
+        <v>6.957</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>7.279</v>
+        <v>7.278</v>
       </c>
       <c r="N32" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="O32" t="n">
         <v>73800000</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>27.3889</v>
+        <v>29.6085</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>7.099</v>
+        <v>7.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4119</v>
+        <v>4132</v>
       </c>
       <c r="O33" t="n">
         <v>150000000</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>16.1477</v>
+        <v>16.313</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6.313</v>
+        <v>6.318</v>
       </c>
       <c r="N34" t="n">
-        <v>3027</v>
+        <v>3033</v>
       </c>
       <c r="O34" t="n">
         <v>297000000</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>20.5353</v>
+        <v>20.4182</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7.532</v>
+        <v>7.533</v>
       </c>
       <c r="N35" t="n">
-        <v>4106</v>
+        <v>4116</v>
       </c>
       <c r="O35" t="n">
         <v>291000000</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>28.6923</v>
+        <v>27.4675</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>7.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3015</v>
+        <v>3021</v>
       </c>
       <c r="O36" t="n">
         <v>80000000</v>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10.3945</v>
+        <v>11.8575</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>8.208</v>
+        <v>8.209</v>
       </c>
       <c r="N37" t="n">
-        <v>4043</v>
+        <v>4051</v>
       </c>
       <c r="O37" t="n">
         <v>15700000</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>11.6245</v>
+        <v>12.5949</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>6.8</v>
       </c>
       <c r="N38" t="n">
-        <v>10571</v>
+        <v>10577</v>
       </c>
       <c r="O38" t="n">
         <v>110000000</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>It’s time to meet Carnage.</t>
+          <t>You are what you eat.</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.5695</v>
+        <v>4.0423</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>19.5832</v>
+        <v>21.0991</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>7.618</v>
       </c>
       <c r="N40" t="n">
-        <v>4734</v>
+        <v>4743</v>
       </c>
       <c r="O40" t="n">
         <v>200000000</v>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>150.0364</v>
+        <v>145.4634</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2297</v>
+        <v>2331</v>
       </c>
       <c r="O41" t="n">
         <v>122000000</v>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>21.7922</v>
+        <v>26.2224</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>8.217000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>8074</v>
+        <v>8089</v>
       </c>
       <c r="O42" t="n">
         <v>90000000</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.6015</v>
+        <v>1.6384</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.4</v>
+        <v>6.385</v>
       </c>
       <c r="N43" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O43" t="n">
         <v>100000000</v>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>84.6773</v>
+        <v>79.9906</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.8</v>
+        <v>6.786</v>
       </c>
       <c r="N44" t="n">
-        <v>3108</v>
+        <v>3126</v>
       </c>
       <c r="O44" t="n">
         <v>120000000</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10.9634</v>
+        <v>10.6881</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>6.295</v>
+        <v>6.294</v>
       </c>
       <c r="N45" t="n">
-        <v>5201</v>
+        <v>5212</v>
       </c>
       <c r="O45" t="n">
         <v>388369742</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1.4358</v>
+        <v>1.5794</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>6.964</v>
+        <v>6.965</v>
       </c>
       <c r="N46" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.297599999999999</v>
+        <v>8.9861</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.579</v>
+        <v>7.578</v>
       </c>
       <c r="N47" t="n">
-        <v>10142</v>
+        <v>10152</v>
       </c>
       <c r="O47" t="n">
         <v>200000000</v>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1.2248</v>
+        <v>0.9452</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.8966</v>
+        <v>1.9397</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.6466</v>
+        <v>0.6876</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/8mjYwWT50GkRrrRdyHzJorfEfcl.jpg</t>
+          <t>/euYIwmwkmz95mnXvufEmbL6ovhZ.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>71.5954</v>
+        <v>71.5707</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>6.765</v>
+        <v>6.8</v>
       </c>
       <c r="N51" t="n">
-        <v>3103</v>
+        <v>3137</v>
       </c>
       <c r="O51" t="n">
         <v>310000000</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>15.2978</v>
+        <v>16.9929</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>7.042</v>
       </c>
       <c r="N52" t="n">
-        <v>2405</v>
+        <v>2421</v>
       </c>
       <c r="O52" t="n">
         <v>100000000</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>20.2842</v>
+        <v>21.5374</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.2</v>
+        <v>7.246</v>
       </c>
       <c r="N53" t="n">
-        <v>4846</v>
+        <v>4857</v>
       </c>
       <c r="O53" t="n">
         <v>195000000</v>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.0149</v>
+        <v>27.9022</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>7.7</v>
+        <v>7.722</v>
       </c>
       <c r="N54" t="n">
-        <v>6932</v>
+        <v>6950</v>
       </c>
       <c r="O54" t="n">
         <v>90000000</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14.852</v>
+        <v>13.0406</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>6.611</v>
       </c>
       <c r="N55" t="n">
-        <v>3004</v>
+        <v>3012</v>
       </c>
       <c r="O55" t="n">
         <v>205000000</v>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[28, 12, 14]</t>
+          <t>[28, 12, 14, 878]</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>15.9028</v>
+        <v>17.2084</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>7.523</v>
+        <v>7.524</v>
       </c>
       <c r="N56" t="n">
-        <v>9642</v>
+        <v>9649</v>
       </c>
       <c r="O56" t="n">
         <v>150000000</v>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>['Action', 'Adventure', 'Fantasy']</t>
+          <t>['Action', 'Adventure', 'Fantasy', 'Science Fiction']</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.1385</v>
+        <v>0.2174</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>12.3445</v>
+        <v>11.5159</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6296,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.134</v>
+        <v>7.133</v>
       </c>
       <c r="N58" t="n">
-        <v>8373</v>
+        <v>8377</v>
       </c>
       <c r="O58" t="n">
         <v>90000000</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>11.9223</v>
+        <v>12.8573</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6400,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="N59" t="n">
-        <v>4476</v>
+        <v>4482</v>
       </c>
       <c r="O59" t="n">
         <v>85000000</v>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>24.7169</v>
+        <v>27.0622</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>7.782</v>
       </c>
       <c r="N60" t="n">
-        <v>13362</v>
+        <v>13377</v>
       </c>
       <c r="O60" t="n">
         <v>165000000</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.9264</v>
+        <v>10.4699</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>6.6</v>
+        <v>6.647</v>
       </c>
       <c r="N61" t="n">
-        <v>4650</v>
+        <v>4654</v>
       </c>
       <c r="O61" t="n">
         <v>200000000</v>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10.6744</v>
+        <v>10.9606</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6712,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6.913</v>
+        <v>6.9</v>
       </c>
       <c r="N62" t="n">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="O62" t="n">
         <v>120000000</v>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>24.2806</v>
+        <v>21.1506</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>7.472</v>
+        <v>7.47</v>
       </c>
       <c r="N63" t="n">
-        <v>5420</v>
+        <v>5431</v>
       </c>
       <c r="O63" t="n">
         <v>110000000</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>36.3891</v>
+        <v>33.9148</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>7.4</v>
+        <v>7.384</v>
       </c>
       <c r="N64" t="n">
-        <v>2814</v>
+        <v>2824</v>
       </c>
       <c r="O64" t="n">
         <v>100000000</v>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.0214</v>
+        <v>13.9837</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7024,10 +7024,10 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6.8</v>
+        <v>6.824</v>
       </c>
       <c r="N65" t="n">
-        <v>8481</v>
+        <v>8490</v>
       </c>
       <c r="O65" t="n">
         <v>200000000</v>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>0.0071</v>
+        <v>0.0658</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>23.8669</v>
+        <v>21.8199</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7220,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>7.1</v>
+        <v>7.082</v>
       </c>
       <c r="N67" t="n">
-        <v>3644</v>
+        <v>3655</v>
       </c>
       <c r="O67" t="n">
         <v>160000000</v>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>11.9891</v>
+        <v>11.0667</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>6.9</v>
       </c>
       <c r="N68" t="n">
-        <v>6479</v>
+        <v>6486</v>
       </c>
       <c r="O68" t="n">
         <v>200000000</v>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.8423</v>
+        <v>0.5366</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>16.1703</v>
+        <v>14.1558</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="N70" t="n">
-        <v>3544</v>
+        <v>3547</v>
       </c>
       <c r="O70" t="n">
         <v>129000000</v>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>10.8733</v>
+        <v>13.5364</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6.559</v>
+        <v>6.557</v>
       </c>
       <c r="N71" t="n">
-        <v>3600</v>
+        <v>3607</v>
       </c>
       <c r="O71" t="n">
         <v>294700000</v>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15.8599</v>
+        <v>13.7094</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7.2</v>
+        <v>7.209</v>
       </c>
       <c r="N72" t="n">
-        <v>10415</v>
+        <v>10423</v>
       </c>
       <c r="O72" t="n">
         <v>200000000</v>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>19.391</v>
+        <v>14.2341</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>6.856</v>
+        <v>6.855</v>
       </c>
       <c r="N73" t="n">
-        <v>2336</v>
+        <v>2351</v>
       </c>
       <c r="O73" t="n">
         <v>155000000</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6.6178</v>
+        <v>7.1543</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>10.1228</v>
+        <v>11.381</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>7.182</v>
       </c>
       <c r="N75" t="n">
-        <v>10149</v>
+        <v>10165</v>
       </c>
       <c r="O75" t="n">
         <v>205000000</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>15.6867</v>
+        <v>12.7934</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -8140,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>7.047</v>
+        <v>7</v>
       </c>
       <c r="N76" t="n">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="O76" t="n">
         <v>25000000</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>35.4648</v>
+        <v>30.168</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>7.214</v>
+        <v>7.2</v>
       </c>
       <c r="N77" t="n">
-        <v>3484</v>
+        <v>3494</v>
       </c>
       <c r="O77" t="n">
         <v>80000000</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0.9338</v>
+        <v>0.5011</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>16.8721</v>
+        <v>16.3521</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>7.027</v>
+        <v>7.028</v>
       </c>
       <c r="N79" t="n">
-        <v>2960</v>
+        <v>2970</v>
       </c>
       <c r="O79" t="n">
         <v>100000000</v>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>1.1791</v>
+        <v>1.3477</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>58.4281</v>
+        <v>61.569</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>8.300000000000001</v>
+        <v>8.333</v>
       </c>
       <c r="N81" t="n">
-        <v>4616</v>
+        <v>4646</v>
       </c>
       <c r="O81" t="n">
         <v>78000000</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8.3955</v>
+        <v>9.32</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -8740,10 +8740,10 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>7.483</v>
+        <v>7.482</v>
       </c>
       <c r="N82" t="n">
-        <v>9007</v>
+        <v>9015</v>
       </c>
       <c r="O82" t="n">
         <v>110000000</v>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6.544</v>
+        <v>7.207</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>7.931</v>
+        <v>7.927</v>
       </c>
       <c r="N83" t="n">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>16.5439</v>
+        <v>17.529</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>7.3</v>
       </c>
       <c r="N84" t="n">
-        <v>9850</v>
+        <v>9854</v>
       </c>
       <c r="O84" t="n">
         <v>85000000</v>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.9018</v>
+        <v>23.5713</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>7.4</v>
       </c>
       <c r="N85" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="O85" t="n">
         <v>72000000</v>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>10.6737</v>
+        <v>9.8797</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>7.5</v>
+        <v>7.473</v>
       </c>
       <c r="N86" t="n">
-        <v>6733</v>
+        <v>6738</v>
       </c>
       <c r="O86" t="n">
         <v>55000000</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>13.6723</v>
+        <v>29.3498</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -9260,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>7.484</v>
+        <v>7.483</v>
       </c>
       <c r="N87" t="n">
-        <v>4270</v>
+        <v>4279</v>
       </c>
       <c r="O87" t="n">
         <v>20000000</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.0707</v>
+        <v>17.6106</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>7.5</v>
+        <v>7.453</v>
       </c>
       <c r="N88" t="n">
-        <v>2104</v>
+        <v>2115</v>
       </c>
       <c r="O88" t="n">
         <v>50000000</v>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.6411</v>
+        <v>5.8518</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>7.5</v>
       </c>
       <c r="N89" t="n">
-        <v>3530</v>
+        <v>3535</v>
       </c>
       <c r="O89" t="n">
         <v>85000000</v>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0.8388</v>
+        <v>0.785</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>8</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="P90" t="n">
         <v>275815986</v>
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>8.0509</v>
+        <v>8.2607</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>7.1</v>
+        <v>7.115</v>
       </c>
       <c r="N91" t="n">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="O91" t="n">
         <v>75000000</v>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>16.0048</v>
+        <v>13.5061</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.662</v>
+        <v>6.659</v>
       </c>
       <c r="N92" t="n">
-        <v>4466</v>
+        <v>4473</v>
       </c>
       <c r="O92" t="n">
         <v>220000000</v>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>15.4765</v>
+        <v>12.4379</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6.711</v>
+        <v>6.712</v>
       </c>
       <c r="N93" t="n">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="O93" t="n">
         <v>38500000</v>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>24.7039</v>
+        <v>21.4216</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>6.741</v>
+        <v>6.739</v>
       </c>
       <c r="N94" t="n">
-        <v>2656</v>
+        <v>2676</v>
       </c>
       <c r="O94" t="n">
         <v>67000000</v>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3.4188</v>
+        <v>4.0925</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>8.259</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="N95" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="O95" t="n">
         <v>15000000</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>17.6489</v>
+        <v>18.0705</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>7.595</v>
       </c>
       <c r="N96" t="n">
-        <v>9658</v>
+        <v>9665</v>
       </c>
       <c r="O96" t="n">
         <v>135000000</v>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>3.9327</v>
+        <v>4.1259</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -10292,10 +10292,10 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>7.749</v>
+        <v>7.741</v>
       </c>
       <c r="N97" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>12.7589</v>
+        <v>13.6666</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -10396,10 +10396,10 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>6.3</v>
+        <v>6.319</v>
       </c>
       <c r="N98" t="n">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="O98" t="n">
         <v>175000000</v>
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>23.5052</v>
+        <v>25.4314</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>7.1</v>
       </c>
       <c r="N99" t="n">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="O99" t="n">
         <v>60000000</v>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.2619</v>
+        <v>0.5192</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -10604,10 +10604,10 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>7.4</v>
+        <v>7.423</v>
       </c>
       <c r="N100" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O100" t="n">
         <v>8800000</v>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>1.3008</v>
+        <v>1.26</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8.1</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>6494</v>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>7.722</v>
+        <v>7.7</v>
       </c>
       <c r="N54" t="n">
         <v>6950</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>7.028</v>
+        <v>7.027</v>
       </c>
       <c r="N79" t="n">
-        <v>2970</v>
+        <v>2972</v>
       </c>
       <c r="O79" t="n">
         <v>100000000</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -711,7 +711,7 @@
         <v>7.946</v>
       </c>
       <c r="N3" t="n">
-        <v>20654</v>
+        <v>20655</v>
       </c>
       <c r="O3" t="n">
         <v>200000000</v>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.556</v>
+        <v>7.557</v>
       </c>
       <c r="N4" t="n">
-        <v>5713</v>
+        <v>5718</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.180999999999999</v>
+        <v>8.182</v>
       </c>
       <c r="N5" t="n">
-        <v>9705</v>
+        <v>9708</v>
       </c>
       <c r="O5" t="n">
         <v>170000000</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>6.982</v>
       </c>
       <c r="N6" t="n">
         <v>9750</v>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.6</v>
+        <v>7.624</v>
       </c>
       <c r="N7" t="n">
-        <v>9568</v>
+        <v>9569</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1227,7 +1227,7 @@
         <v>7.608</v>
       </c>
       <c r="N8" t="n">
-        <v>7000</v>
+        <v>7003</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.108</v>
+        <v>7.104</v>
       </c>
       <c r="N9" t="n">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.051</v>
+        <v>7.052</v>
       </c>
       <c r="N11" t="n">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="O11" t="n">
         <v>100000000</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.264</v>
+        <v>7.3</v>
       </c>
       <c r="N12" t="n">
         <v>9452</v>
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1</v>
+        <v>8.067</v>
       </c>
       <c r="N13" t="n">
-        <v>10057</v>
+        <v>10058</v>
       </c>
       <c r="O13" t="n">
         <v>100000000</v>
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.3</v>
+        <v>7.301</v>
       </c>
       <c r="N14" t="n">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
@@ -2435,7 +2435,7 @@
         <v>7.655</v>
       </c>
       <c r="N20" t="n">
-        <v>10785</v>
+        <v>10787</v>
       </c>
       <c r="O20" t="n">
         <v>185000000</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.933</v>
+        <v>6.934</v>
       </c>
       <c r="N22" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="O22" t="n">
         <v>150000000</v>
@@ -2844,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.444</v>
+        <v>7.443</v>
       </c>
       <c r="N24" t="n">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="O24" t="n">
         <v>200000000</v>
@@ -3159,7 +3159,7 @@
         <v>8.345000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>7450</v>
+        <v>7453</v>
       </c>
       <c r="O27" t="n">
         <v>100000000</v>
@@ -3956,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7.533</v>
+        <v>7.5</v>
       </c>
       <c r="N35" t="n">
-        <v>4116</v>
+        <v>4117</v>
       </c>
       <c r="O35" t="n">
         <v>291000000</v>
@@ -4060,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="O36" t="n">
         <v>80000000</v>
@@ -4164,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>8.209</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="O37" t="n">
         <v>15700000</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6.8</v>
+        <v>6.777</v>
       </c>
       <c r="N38" t="n">
-        <v>10577</v>
+        <v>10578</v>
       </c>
       <c r="O38" t="n">
         <v>110000000</v>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>7.618</v>
+        <v>7.6</v>
       </c>
       <c r="N40" t="n">
         <v>4743</v>
@@ -4576,10 +4576,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.8</v>
+        <v>7.764</v>
       </c>
       <c r="N41" t="n">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="O41" t="n">
         <v>122000000</v>
@@ -4680,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>8.217000000000001</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="O42" t="n">
         <v>90000000</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.786</v>
+        <v>6.785</v>
       </c>
       <c r="N44" t="n">
-        <v>3126</v>
+        <v>3128</v>
       </c>
       <c r="O44" t="n">
         <v>120000000</v>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.578</v>
+        <v>7.577</v>
       </c>
       <c r="N47" t="n">
-        <v>10152</v>
+        <v>10153</v>
       </c>
       <c r="O47" t="n">
         <v>200000000</v>
@@ -5576,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>6.8</v>
+        <v>6.761</v>
       </c>
       <c r="N51" t="n">
-        <v>3137</v>
+        <v>3139</v>
       </c>
       <c r="O51" t="n">
         <v>310000000</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/vchI0KSlYgCInkAdBlDaxL9xhq5.jpg</t>
+          <t>/xi1VSt3DtkevUmzCx2mNlCoDe74.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>/9utRLSrJ7Jn9YoeUJpeNPCWeI6t.jpg</t>
+          <t>/kWJw7dCWHcfMLr0irTHAPIKrJ4I.jpg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7.042</v>
+        <v>7</v>
       </c>
       <c r="N52" t="n">
         <v>2421</v>
@@ -6099,7 +6099,7 @@
         <v>7.524</v>
       </c>
       <c r="N56" t="n">
-        <v>9649</v>
+        <v>9650</v>
       </c>
       <c r="O56" t="n">
         <v>150000000</v>
@@ -6299,7 +6299,7 @@
         <v>7.133</v>
       </c>
       <c r="N58" t="n">
-        <v>8377</v>
+        <v>8378</v>
       </c>
       <c r="O58" t="n">
         <v>90000000</v>
@@ -6400,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.85</v>
+        <v>7.849</v>
       </c>
       <c r="N59" t="n">
-        <v>4482</v>
+        <v>4483</v>
       </c>
       <c r="O59" t="n">
         <v>85000000</v>
@@ -6507,7 +6507,7 @@
         <v>7.782</v>
       </c>
       <c r="N60" t="n">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="O60" t="n">
         <v>165000000</v>
@@ -6712,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6.9</v>
+        <v>6.915</v>
       </c>
       <c r="N62" t="n">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="O62" t="n">
         <v>120000000</v>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>7.384</v>
+        <v>7.383</v>
       </c>
       <c r="N64" t="n">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="O64" t="n">
         <v>100000000</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6.557</v>
+        <v>6.556</v>
       </c>
       <c r="N71" t="n">
-        <v>3607</v>
+        <v>3609</v>
       </c>
       <c r="O71" t="n">
         <v>294700000</v>
@@ -7839,7 +7839,7 @@
         <v>6.855</v>
       </c>
       <c r="N73" t="n">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="O73" t="n">
         <v>155000000</v>
@@ -8140,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="N76" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="O76" t="n">
         <v>25000000</v>
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
       <c r="N77" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="O77" t="n">
         <v>80000000</v>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>8.333</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>4646</v>
+        <v>4649</v>
       </c>
       <c r="O81" t="n">
         <v>78000000</v>
@@ -8743,7 +8743,7 @@
         <v>7.482</v>
       </c>
       <c r="N82" t="n">
-        <v>9015</v>
+        <v>9016</v>
       </c>
       <c r="O82" t="n">
         <v>110000000</v>
@@ -8844,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>7.927</v>
+        <v>7.926</v>
       </c>
       <c r="N83" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -9260,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>7.483</v>
+        <v>7.484</v>
       </c>
       <c r="N87" t="n">
-        <v>4279</v>
+        <v>4281</v>
       </c>
       <c r="O87" t="n">
         <v>20000000</v>
@@ -9772,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.659</v>
+        <v>6.66</v>
       </c>
       <c r="N92" t="n">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="O92" t="n">
         <v>220000000</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>6.739</v>
+        <v>6.738</v>
       </c>
       <c r="N94" t="n">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="O94" t="n">
         <v>67000000</v>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>8.226000000000001</v>
+        <v>8.227</v>
       </c>
       <c r="N95" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O95" t="n">
         <v>15000000</v>
@@ -10399,7 +10399,7 @@
         <v>6.319</v>
       </c>
       <c r="N98" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="O98" t="n">
         <v>175000000</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -1019,7 +1019,7 @@
         <v>6.982</v>
       </c>
       <c r="N6" t="n">
-        <v>9750</v>
+        <v>9751</v>
       </c>
       <c r="O6" t="n">
         <v>145000000</v>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8.148999999999999</v>
+        <v>8.148</v>
       </c>
       <c r="N25" t="n">
-        <v>6494</v>
+        <v>6498</v>
       </c>
       <c r="O25" t="n">
         <v>190000000</v>
@@ -7223,7 +7223,7 @@
         <v>7.082</v>
       </c>
       <c r="N67" t="n">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="O67" t="n">
         <v>160000000</v>
@@ -8039,7 +8039,7 @@
         <v>7.182</v>
       </c>
       <c r="N75" t="n">
-        <v>10165</v>
+        <v>10166</v>
       </c>
       <c r="O75" t="n">
         <v>205000000</v>
@@ -10191,7 +10191,7 @@
         <v>7.595</v>
       </c>
       <c r="N96" t="n">
-        <v>9665</v>
+        <v>9669</v>
       </c>
       <c r="O96" t="n">
         <v>135000000</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -815,7 +815,7 @@
         <v>7.557</v>
       </c>
       <c r="N4" t="n">
-        <v>5718</v>
+        <v>5720</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.182</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9708</v>
+        <v>9709</v>
       </c>
       <c r="O5" t="n">
         <v>170000000</v>
@@ -1123,7 +1123,7 @@
         <v>7.624</v>
       </c>
       <c r="N7" t="n">
-        <v>9569</v>
+        <v>9570</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1227,7 +1227,7 @@
         <v>7.608</v>
       </c>
       <c r="N8" t="n">
-        <v>7003</v>
+        <v>7005</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.104</v>
+        <v>7.082</v>
       </c>
       <c r="N9" t="n">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.7</v>
+        <v>6.668</v>
       </c>
       <c r="N10" t="n">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="O10" t="n">
         <v>165000000</v>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.052</v>
+        <v>7.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="O11" t="n">
         <v>100000000</v>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.3</v>
+        <v>7.264</v>
       </c>
       <c r="N12" t="n">
-        <v>9452</v>
+        <v>9453</v>
       </c>
       <c r="O12" t="n">
         <v>200000000</v>
@@ -2135,7 +2135,7 @@
         <v>7.948</v>
       </c>
       <c r="N17" t="n">
-        <v>7242</v>
+        <v>7243</v>
       </c>
       <c r="O17" t="n">
         <v>250000000</v>
@@ -2536,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.42</v>
+        <v>6.421</v>
       </c>
       <c r="N21" t="n">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="O21" t="n">
         <v>250000000</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.934</v>
+        <v>6.931</v>
       </c>
       <c r="N22" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="O22" t="n">
         <v>150000000</v>
@@ -2844,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.443</v>
+        <v>7.415</v>
       </c>
       <c r="N24" t="n">
-        <v>1864</v>
+        <v>1877</v>
       </c>
       <c r="O24" t="n">
         <v>200000000</v>
@@ -3052,10 +3052,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7.049</v>
+        <v>7.048</v>
       </c>
       <c r="N26" t="n">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="O26" t="n">
         <v>340000000</v>
@@ -3448,10 +3448,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7.086</v>
+        <v>7.085</v>
       </c>
       <c r="N30" t="n">
-        <v>3823</v>
+        <v>3825</v>
       </c>
       <c r="O30" t="n">
         <v>125000000</v>
@@ -3748,10 +3748,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>7.1</v>
+        <v>7.098</v>
       </c>
       <c r="N33" t="n">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="O33" t="n">
         <v>150000000</v>
@@ -3956,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7.5</v>
+        <v>7.534</v>
       </c>
       <c r="N35" t="n">
-        <v>4117</v>
+        <v>4118</v>
       </c>
       <c r="O35" t="n">
         <v>291000000</v>
@@ -4271,7 +4271,7 @@
         <v>6.777</v>
       </c>
       <c r="N38" t="n">
-        <v>10578</v>
+        <v>10579</v>
       </c>
       <c r="O38" t="n">
         <v>110000000</v>
@@ -4576,10 +4576,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.764</v>
+        <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="O41" t="n">
         <v>122000000</v>
@@ -4683,7 +4683,7 @@
         <v>8.215999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>8090</v>
+        <v>8091</v>
       </c>
       <c r="O42" t="n">
         <v>90000000</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.785</v>
+        <v>6.786</v>
       </c>
       <c r="N44" t="n">
-        <v>3128</v>
+        <v>3132</v>
       </c>
       <c r="O44" t="n">
         <v>120000000</v>
@@ -4991,7 +4991,7 @@
         <v>6.294</v>
       </c>
       <c r="N45" t="n">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="O45" t="n">
         <v>388369742</v>
@@ -5579,7 +5579,7 @@
         <v>6.761</v>
       </c>
       <c r="N51" t="n">
-        <v>3139</v>
+        <v>3141</v>
       </c>
       <c r="O51" t="n">
         <v>310000000</v>
@@ -5680,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>7.041</v>
       </c>
       <c r="N52" t="n">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="O52" t="n">
         <v>100000000</v>
@@ -5888,10 +5888,10 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>7.7</v>
+        <v>7.722</v>
       </c>
       <c r="N54" t="n">
-        <v>6950</v>
+        <v>6952</v>
       </c>
       <c r="O54" t="n">
         <v>90000000</v>
@@ -6099,7 +6099,7 @@
         <v>7.524</v>
       </c>
       <c r="N56" t="n">
-        <v>9650</v>
+        <v>9651</v>
       </c>
       <c r="O56" t="n">
         <v>150000000</v>
@@ -6507,7 +6507,7 @@
         <v>7.782</v>
       </c>
       <c r="N60" t="n">
-        <v>13378</v>
+        <v>13380</v>
       </c>
       <c r="O60" t="n">
         <v>165000000</v>
@@ -6819,7 +6819,7 @@
         <v>7.47</v>
       </c>
       <c r="N63" t="n">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="O63" t="n">
         <v>110000000</v>
@@ -6923,7 +6923,7 @@
         <v>7.383</v>
       </c>
       <c r="N64" t="n">
-        <v>2826</v>
+        <v>2829</v>
       </c>
       <c r="O64" t="n">
         <v>100000000</v>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7.209</v>
+        <v>7.2</v>
       </c>
       <c r="N72" t="n">
         <v>10423</v>
@@ -7839,7 +7839,7 @@
         <v>6.855</v>
       </c>
       <c r="N73" t="n">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="O73" t="n">
         <v>155000000</v>
@@ -8140,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>7.05</v>
+        <v>7.049</v>
       </c>
       <c r="N76" t="n">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="O76" t="n">
         <v>25000000</v>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>8.332000000000001</v>
+        <v>8.333</v>
       </c>
       <c r="N81" t="n">
-        <v>4649</v>
+        <v>4653</v>
       </c>
       <c r="O81" t="n">
         <v>78000000</v>
@@ -9159,7 +9159,7 @@
         <v>7.473</v>
       </c>
       <c r="N86" t="n">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="O86" t="n">
         <v>55000000</v>
@@ -9263,7 +9263,7 @@
         <v>7.484</v>
       </c>
       <c r="N87" t="n">
-        <v>4281</v>
+        <v>4282</v>
       </c>
       <c r="O87" t="n">
         <v>20000000</v>
@@ -9364,10 +9364,10 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>7.453</v>
+        <v>7.454</v>
       </c>
       <c r="N88" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="O88" t="n">
         <v>50000000</v>
@@ -9671,7 +9671,7 @@
         <v>7.115</v>
       </c>
       <c r="N91" t="n">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="O91" t="n">
         <v>75000000</v>
@@ -9876,10 +9876,10 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>6.712</v>
+        <v>6.713</v>
       </c>
       <c r="N93" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="O93" t="n">
         <v>38500000</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>6.738</v>
+        <v>6.739</v>
       </c>
       <c r="N94" t="n">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="O94" t="n">
         <v>67000000</v>

--- a/src/static/xlsx/tmdb_movies.xlsx
+++ b/src/static/xlsx/tmdb_movies.xlsx
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.301</v>
+        <v>7.302</v>
       </c>
       <c r="N14" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
